--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="29" activeTab="29"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="54" activeTab="54"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="358">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -1020,9 +1020,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>26550</t>
-  </si>
-  <si>
     <t>BRSPSIE</t>
   </si>
   <si>
@@ -1083,100 +1080,92 @@
     <t>00469</t>
   </si>
   <si>
+    <t>SUP10388</t>
+  </si>
+  <si>
+    <t>AFT PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>AFT PRIVATE LIMITED(AP)</t>
+  </si>
+  <si>
+    <t>DirectGrnGenUDIMP</t>
+  </si>
+  <si>
+    <t>DirectGrnGenUDMultiIMP</t>
+  </si>
+  <si>
+    <t>WALMART(AP)</t>
+  </si>
+  <si>
+    <t>SUP00375</t>
+  </si>
+  <si>
+    <t>WALMART</t>
+  </si>
+  <si>
+    <t>BANK CHARGES</t>
+  </si>
+  <si>
+    <t>Charges Flag</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>GERERAL</t>
+  </si>
+  <si>
+    <t>ADMINISTRATION EXPENSES</t>
+  </si>
+  <si>
+    <t>INTEREST INCOME ON LOAN</t>
+  </si>
+  <si>
+    <t>00856</t>
+  </si>
+  <si>
+    <t>Cr.</t>
+  </si>
+  <si>
+    <t>Dr.</t>
+  </si>
+  <si>
+    <t>HARITRADERS</t>
+  </si>
+  <si>
+    <t>34AWPPH5612QIJY</t>
+  </si>
+  <si>
+    <t>GSTIN</t>
+  </si>
+  <si>
+    <t>GST SUPPLIER NAME</t>
+  </si>
+  <si>
+    <t>82.5</t>
+  </si>
+  <si>
+    <t>194C(TDS)</t>
+  </si>
+  <si>
+    <t>TDS %</t>
+  </si>
+  <si>
+    <t>TDS AMT</t>
+  </si>
+  <si>
     <t>666.3</t>
-  </si>
-  <si>
-    <t>666.66</t>
-  </si>
-  <si>
-    <t>SUP10388</t>
-  </si>
-  <si>
-    <t>AFT PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>AFT PRIVATE LIMITED(AP)</t>
-  </si>
-  <si>
-    <t>DirectGrnGenUDIMP</t>
-  </si>
-  <si>
-    <t>DirectGrnGenUDMultiIMP</t>
-  </si>
-  <si>
-    <t>WALMART(AP)</t>
-  </si>
-  <si>
-    <t>SUP00375</t>
-  </si>
-  <si>
-    <t>WALMART</t>
-  </si>
-  <si>
-    <t>BANK CHARGES</t>
-  </si>
-  <si>
-    <t>Charges Flag</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>GERERAL</t>
-  </si>
-  <si>
-    <t>ADMINISTRATION EXPENSES</t>
-  </si>
-  <si>
-    <t>INTEREST INCOME ON LOAN</t>
-  </si>
-  <si>
-    <t>00856</t>
-  </si>
-  <si>
-    <t>Cr.</t>
-  </si>
-  <si>
-    <t>Dr.</t>
-  </si>
-  <si>
-    <t>HARITRADERS</t>
-  </si>
-  <si>
-    <t>34AWPPH5612QIJY</t>
-  </si>
-  <si>
-    <t>GSTIN</t>
-  </si>
-  <si>
-    <t>GST SUPPLIER NAME</t>
-  </si>
-  <si>
-    <t>1650</t>
-  </si>
-  <si>
-    <t>82.5</t>
-  </si>
-  <si>
-    <t>194C(TDS)</t>
-  </si>
-  <si>
-    <t>TDS %</t>
-  </si>
-  <si>
-    <t>TDS AMT</t>
-  </si>
-  <si>
-    <t>56.46</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
       <sz val="11"/>
@@ -2100,15 +2089,15 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.7109375"/>
+    <col min="2" max="3" customWidth="true" width="12.7109375"/>
+    <col min="4" max="4" customWidth="true" width="14.7109375"/>
+    <col min="5" max="5" customWidth="true" width="9.85546875"/>
+    <col min="6" max="6" customWidth="true" width="14.140625"/>
+    <col min="7" max="7" customWidth="true" width="14.85546875"/>
+    <col min="8" max="8" customWidth="true" width="22.28515625"/>
+    <col min="9" max="9" customWidth="true" width="14.42578125"/>
+    <col min="10" max="10" customWidth="true" width="13.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2441,17 +2430,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="28.5703125" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="9.0"/>
+    <col min="2" max="2" customWidth="true" width="25.7109375"/>
+    <col min="3" max="3" customWidth="true" width="12.42578125"/>
+    <col min="4" max="4" customWidth="true" width="16.28515625"/>
+    <col min="5" max="5" customWidth="true" width="20.28515625"/>
+    <col min="6" max="6" customWidth="true" width="25.7109375"/>
+    <col min="7" max="7" customWidth="true" width="12.28515625"/>
+    <col min="8" max="8" customWidth="true" width="14.5703125"/>
+    <col min="9" max="9" customWidth="true" width="28.5703125"/>
+    <col min="10" max="10" customWidth="true" width="23.0"/>
+    <col min="11" max="11" customWidth="true" width="14.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2674,11 +2663,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="13.5703125"/>
+    <col min="2" max="2" customWidth="true" width="6.0"/>
+    <col min="3" max="3" customWidth="true" width="14.42578125"/>
+    <col min="4" max="4" customWidth="true" width="18.140625"/>
+    <col min="5" max="5" customWidth="true" width="19.5703125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2759,13 +2748,13 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="25.7109375"/>
+    <col min="2" max="2" customWidth="true" width="8.85546875"/>
+    <col min="3" max="3" customWidth="true" width="12.28515625"/>
+    <col min="4" max="4" customWidth="true" width="7.140625"/>
+    <col min="5" max="5" customWidth="true" width="5.28515625"/>
+    <col min="6" max="6" customWidth="true" width="17.42578125"/>
+    <col min="7" max="7" customWidth="true" width="12.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3100,9 +3089,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="25.5703125"/>
+    <col min="2" max="2" customWidth="true" width="15.140625"/>
+    <col min="3" max="3" customWidth="true" width="16.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3148,12 +3137,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
+    <col min="2" max="2" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="5" max="5" customWidth="true" width="19.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3186,13 +3175,13 @@
       <c r="C2" s="1">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>249</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>251</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <f>ROUND(C2*E2,2)</f>
         <v>847.48</v>
       </c>
@@ -3207,13 +3196,13 @@
       <c r="C3" s="1">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <f>ROUND(C3*E3,2)</f>
         <v>159.26</v>
       </c>
@@ -3228,9 +3217,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="21.42578125"/>
+    <col min="2" max="2" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" customWidth="true" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3276,7 +3265,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3451,26 +3440,26 @@
   <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
-    <col min="8" max="8" width="26.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="29.5703125" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" customWidth="1"/>
-    <col min="17" max="17" width="17.7109375" customWidth="1"/>
-    <col min="18" max="18" width="24.140625" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="30.0"/>
+    <col min="2" max="2" customWidth="true" width="36.42578125"/>
+    <col min="3" max="3" customWidth="true" width="6.0"/>
+    <col min="4" max="4" customWidth="true" width="13.7109375"/>
+    <col min="5" max="5" customWidth="true" width="5.28515625"/>
+    <col min="6" max="6" customWidth="true" width="17.28515625"/>
+    <col min="7" max="7" customWidth="true" width="30.28515625"/>
+    <col min="8" max="8" customWidth="true" width="26.85546875"/>
+    <col min="9" max="9" customWidth="true" width="17.28515625"/>
+    <col min="10" max="10" customWidth="true" width="13.28515625"/>
+    <col min="11" max="11" customWidth="true" width="22.7109375"/>
+    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="13" max="13" customWidth="true" width="29.5703125"/>
+    <col min="14" max="14" customWidth="true" width="18.28515625"/>
+    <col min="15" max="15" customWidth="true" width="16.28515625"/>
+    <col min="16" max="16" customWidth="true" width="15.5703125"/>
+    <col min="17" max="17" customWidth="true" width="17.7109375"/>
+    <col min="18" max="18" customWidth="true" width="24.140625"/>
+    <col min="19" max="19" customWidth="true" width="13.42578125"/>
+    <col min="20" max="20" customWidth="true" width="13.5703125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3764,7 +3753,7 @@
       <c r="D6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>5</v>
       </c>
       <c r="F6" s="27" t="s">
@@ -4032,7 +4021,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>234</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -4043,18 +4032,18 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>45</v>
       </c>
     </row>
@@ -4068,25 +4057,25 @@
   <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
+    <col min="3" max="3" customWidth="true" width="22.140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4164,19 +4153,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4185,16 +4174,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>2000</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>1</v>
       </c>
     </row>
@@ -4202,19 +4191,19 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>284</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>274</v>
       </c>
       <c r="G3" s="39" t="s">
@@ -4223,16 +4212,16 @@
       <c r="H3" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <v>2000</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <v>1</v>
       </c>
     </row>
@@ -4357,25 +4346,25 @@
   <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
+    <col min="3" max="3" customWidth="true" width="22.140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4453,19 +4442,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4474,16 +4463,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>2000</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>1</v>
       </c>
     </row>
@@ -4556,25 +4545,25 @@
   <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
+    <col min="3" max="3" customWidth="true" width="22.140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4652,19 +4641,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4673,16 +4662,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>2000</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>1</v>
       </c>
     </row>
@@ -4755,23 +4744,23 @@
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="8.28515625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -4895,7 +4884,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4954,27 +4943,27 @@
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="16.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5126,10 +5115,10 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" t="s" s="0">
         <v>298</v>
       </c>
     </row>
@@ -5144,27 +5133,27 @@
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="16.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5316,10 +5305,10 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" t="s" s="0">
         <v>298</v>
       </c>
     </row>
@@ -5334,34 +5323,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5402,10 +5391,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -5444,13 +5433,13 @@
         <v>306</v>
       </c>
       <c r="AA1" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB1" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="AB1" s="40" t="s">
+      <c r="AC1" s="40" t="s">
         <v>329</v>
-      </c>
-      <c r="AC1" s="40" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -5458,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -5470,10 +5459,10 @@
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -5487,8 +5476,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -5519,37 +5508,37 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -5565,34 +5554,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5633,10 +5622,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -5689,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -5701,10 +5690,10 @@
         <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -5718,8 +5707,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -5727,7 +5716,7 @@
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -5750,33 +5739,33 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
-        <v>1332.6</v>
-      </c>
-      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5790,34 +5779,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5858,10 +5847,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -5914,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -5926,10 +5915,10 @@
         <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -5943,8 +5932,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -5975,13 +5964,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>1000</v>
       </c>
@@ -5991,25 +5980,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I3" s="1">
         <v>1000</v>
@@ -6020,8 +6009,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -6052,35 +6041,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>2000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>2000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>2000</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>2000</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>2000</v>
       </c>
@@ -6096,17 +6085,17 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="21.0"/>
+    <col min="3" max="3" customWidth="true" width="6.0"/>
+    <col min="4" max="4" customWidth="true" width="12.7109375"/>
+    <col min="5" max="5" customWidth="true" width="19.42578125"/>
+    <col min="6" max="6" customWidth="true" width="15.140625"/>
+    <col min="7" max="7" customWidth="true" width="15.42578125"/>
+    <col min="8" max="8" customWidth="true" width="19.5703125"/>
+    <col min="9" max="9" customWidth="true" width="10.85546875"/>
+    <col min="10" max="10" customWidth="true" width="17.5703125"/>
+    <col min="11" max="11" customWidth="true" width="11.28515625"/>
+    <col min="12" max="12" customWidth="true" width="21.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6245,34 +6234,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6313,10 +6302,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -6369,7 +6358,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -6381,10 +6370,10 @@
         <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -6398,8 +6387,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -6430,13 +6419,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -6446,25 +6435,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -6475,8 +6464,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -6507,35 +6496,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -6551,34 +6540,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6619,10 +6608,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -6675,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -6687,10 +6676,10 @@
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -6704,8 +6693,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -6736,13 +6725,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -6752,22 +6741,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>275</v>
@@ -6781,8 +6770,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -6813,35 +6802,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC3">
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -6857,34 +6846,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6925,10 +6914,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -6967,13 +6956,13 @@
         <v>306</v>
       </c>
       <c r="AA1" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB1" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="AB1" s="40" t="s">
+      <c r="AC1" s="40" t="s">
         <v>329</v>
-      </c>
-      <c r="AC1" s="40" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -6981,22 +6970,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -7010,8 +6999,8 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -7042,37 +7031,37 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -7088,29 +7077,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -7202,7 +7191,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -7210,22 +7199,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -7239,8 +7228,8 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>357</v>
+      <c r="L2" t="s" s="0">
+        <v>353</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -7271,18 +7260,18 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -7290,16 +7279,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="1">
@@ -7311,8 +7300,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -7343,43 +7332,43 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>10</v>
       </c>
-      <c r="AD3" t="s">
-        <v>345</v>
+      <c r="AD3" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
         <v>-10</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
         <v>-10</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>10</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-10</v>
       </c>
-      <c r="AD4" t="s">
-        <v>345</v>
+      <c r="AD4" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -7393,29 +7382,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -7507,7 +7496,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -7515,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -7527,10 +7516,10 @@
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -7544,22 +7533,22 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>666.3</v>
+        <v>0</v>
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>666.3</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
         <f>M2</f>
-        <v>666.3</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -7576,18 +7565,18 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>666.3</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>344</v>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -7595,16 +7584,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="1">
@@ -7616,8 +7605,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -7648,43 +7637,43 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>100</v>
       </c>
-      <c r="AD3" t="s">
-        <v>345</v>
+      <c r="AD3" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>100</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
-        <v>566.29999999999995</v>
-      </c>
-      <c r="N4">
+        <v>-100</v>
+      </c>
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
-        <v>566.29999999999995</v>
-      </c>
-      <c r="Q4">
+        <v>-100</v>
+      </c>
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
-        <v>766.3</v>
-      </c>
-      <c r="AC4">
+        <v>100</v>
+      </c>
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
-        <v>566.29999999999995</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>345</v>
+        <v>-100</v>
+      </c>
+      <c r="AD4" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -7698,34 +7687,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -7766,10 +7755,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -7822,22 +7811,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -7851,8 +7840,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -7883,31 +7872,31 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -7923,34 +7912,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -7991,10 +7980,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -8047,22 +8036,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -8076,8 +8065,8 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -8108,13 +8097,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -8124,22 +8113,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>275</v>
@@ -8153,8 +8142,8 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -8185,35 +8174,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -8229,34 +8218,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="24.140625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -8297,10 +8286,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -8353,22 +8342,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -8382,22 +8371,22 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
         <f>M2</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -8414,15 +8403,15 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>1332.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8430,25 +8419,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -8459,22 +8448,22 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
-        <v>1333.32</v>
+        <v>0</v>
       </c>
       <c r="N3" s="38">
         <f>AC3</f>
-        <v>1333.32</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1">
         <f>M3</f>
-        <v>1333.32</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -8491,37 +8480,37 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
-        <v>1333.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
-        <v>2665.92</v>
-      </c>
-      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
-        <v>2665.92</v>
-      </c>
-      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
-        <v>2665.92</v>
-      </c>
-      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
-        <v>2665.92</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8535,34 +8524,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="24.140625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -8603,10 +8592,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -8659,22 +8648,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -8688,22 +8677,22 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>1432.6</v>
+        <v>100</v>
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>1432.6</v>
+        <v>100</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
         <f>M2</f>
-        <v>1432.6</v>
+        <v>100</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -8720,15 +8709,15 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>1432.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8736,25 +8725,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I3" s="1">
         <v>100</v>
@@ -8765,22 +8754,22 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
-        <v>1433.32</v>
+        <v>100</v>
       </c>
       <c r="N3" s="38">
         <f>AC3</f>
-        <v>1433.32</v>
+        <v>100</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1">
         <f>M3</f>
-        <v>1433.32</v>
+        <v>100</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -8797,37 +8786,37 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
-        <v>1433.32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>200</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
-        <v>2865.92</v>
-      </c>
-      <c r="N4">
+        <v>200</v>
+      </c>
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
-        <v>2865.92</v>
-      </c>
-      <c r="Q4">
+        <v>200</v>
+      </c>
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
-        <v>2865.92</v>
-      </c>
-      <c r="AC4">
+        <v>200</v>
+      </c>
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
-        <v>2865.92</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -8841,9 +8830,9 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="24.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8899,12 +8888,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.140625"/>
+    <col min="2" max="2" customWidth="true" width="10.42578125"/>
+    <col min="3" max="3" customWidth="true" width="11.42578125"/>
+    <col min="4" max="4" customWidth="true" width="11.7109375"/>
+    <col min="5" max="5" customWidth="true" width="14.5703125"/>
+    <col min="6" max="6" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8975,26 +8964,26 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9091,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -9103,10 +9092,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -9120,8 +9109,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>I2*L2</f>
@@ -9152,27 +9141,27 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM(AA2+AB2),2)</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9186,28 +9175,28 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9304,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -9316,10 +9305,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -9333,8 +9322,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -9365,37 +9354,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -9411,34 +9400,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9535,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -9547,10 +9536,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -9564,8 +9553,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -9596,13 +9585,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -9612,7 +9601,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>179</v>
@@ -9624,10 +9613,10 @@
         <v>302</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>301</v>
@@ -9641,8 +9630,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -9665,31 +9654,31 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -9705,34 +9694,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9773,10 +9762,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -9829,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>161</v>
@@ -9838,13 +9827,13 @@
         <v>162</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -9858,8 +9847,8 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>313</v>
+      <c r="L2" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -9890,37 +9879,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -9936,34 +9925,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10004,10 +9993,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -10060,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>161</v>
@@ -10069,13 +10058,13 @@
         <v>162</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>275</v>
@@ -10089,8 +10078,8 @@
       <c r="K2" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>313</v>
+      <c r="L2" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M2" s="45">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -10121,13 +10110,13 @@
       <c r="Z2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>283500</v>
       </c>
@@ -10137,22 +10126,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>301</v>
@@ -10166,8 +10155,8 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s">
-        <v>313</v>
+      <c r="L3" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -10198,10 +10187,10 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -10210,31 +10199,31 @@
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>400</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>7000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>567000</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>7000</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="0">
         <f>SUM(AA2:AA3)</f>
         <v>0</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="0">
         <f>SUM(AB2:AB3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>567000</v>
       </c>
@@ -10250,34 +10239,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10318,10 +10307,10 @@
         <v>262</v>
       </c>
       <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>314</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>264</v>
@@ -10374,7 +10363,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>161</v>
@@ -10383,13 +10372,13 @@
         <v>162</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>275</v>
@@ -10403,8 +10392,8 @@
       <c r="K2" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>313</v>
+      <c r="L2" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M2" s="45">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -10435,13 +10424,13 @@
       <c r="Z2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -10451,22 +10440,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>301</v>
@@ -10480,8 +10469,8 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s">
-        <v>313</v>
+      <c r="L3" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -10512,10 +10501,10 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -10524,31 +10513,31 @@
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="0">
         <f>SUM(AA2:AA3)</f>
         <v>0</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="0">
         <f>SUM(AB2:AB3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -10564,34 +10553,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10688,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -10700,10 +10689,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>275</v>
@@ -10717,8 +10706,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -10749,13 +10738,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>1000</v>
       </c>
@@ -10765,7 +10754,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>179</v>
@@ -10777,10 +10766,10 @@
         <v>302</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>301</v>
@@ -10794,8 +10783,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -10818,31 +10807,31 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>2000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2:M3)</f>
         <v>2000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2:N3)</f>
         <v>2000</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
         <v>2000</v>
       </c>
@@ -10858,34 +10847,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11043,15 +11032,15 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM(AA2+AB2),2)</f>
-        <v>53100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="1" customFormat="1">
@@ -11109,21 +11098,21 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM(AA3+AB3),2)</f>
-        <v>53100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
-        <v>106200</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11137,34 +11126,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11322,15 +11311,15 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>54100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="1" customFormat="1">
@@ -11388,21 +11377,21 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC3">
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
-        <v>54100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>SUM(AC2:AC3)</f>
-        <v>108200</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -11416,28 +11405,28 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11534,7 +11523,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -11546,10 +11535,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -11563,8 +11552,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -11595,37 +11584,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>10000</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>10000</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>10000</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>10000</v>
       </c>
@@ -11641,12 +11630,12 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.140625"/>
+    <col min="2" max="2" customWidth="true" width="10.42578125"/>
+    <col min="3" max="3" customWidth="true" width="11.42578125"/>
+    <col min="4" max="4" customWidth="true" width="11.7109375"/>
+    <col min="5" max="5" customWidth="true" width="14.5703125"/>
+    <col min="6" max="6" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -11735,29 +11724,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -11849,7 +11838,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -11857,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>161</v>
@@ -11866,13 +11855,13 @@
         <v>162</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -11886,22 +11875,22 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s">
-        <v>313</v>
+      <c r="L2" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>133650</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
         <f>M2</f>
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -11918,18 +11907,18 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>133650</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>344</v>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -11937,16 +11926,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="1">
@@ -11958,7 +11947,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <v>1</v>
       </c>
       <c r="M3" s="38">
@@ -11990,43 +11979,43 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s">
-        <v>345</v>
+      <c r="AD3" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>1000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
-        <v>650</v>
-      </c>
-      <c r="N4">
+        <v>-1000</v>
+      </c>
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
-        <v>132650</v>
-      </c>
-      <c r="Q4">
+        <v>-1000</v>
+      </c>
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
-        <v>2650</v>
-      </c>
-      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
-        <v>132650</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>345</v>
+        <v>-1000</v>
+      </c>
+      <c r="AD4" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -12040,29 +12029,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -12154,7 +12143,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -12162,7 +12151,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -12174,10 +12163,10 @@
         <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -12191,8 +12180,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -12223,18 +12212,18 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -12242,16 +12231,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="1">
@@ -12263,8 +12252,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -12295,43 +12284,43 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s">
-        <v>345</v>
+      <c r="AD3" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>1000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>1000</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="AD4" t="s">
-        <v>345</v>
+      <c r="AD4" t="s" s="0">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -12345,32 +12334,32 @@
   <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -12462,16 +12451,16 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="0">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:33">
@@ -12479,19 +12468,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I2" s="1">
         <v>1000</v>
@@ -12502,8 +12491,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -12552,70 +12541,70 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE2" s="0">
         <v>34</v>
       </c>
-      <c r="AF2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>353</v>
+      <c r="AF2" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
-      <c r="I3">
+      <c r="I3" s="0">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2+R2+S2+T2+U2+W2)</f>
         <v>1180</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2+R2+S2+T2+U2+W2)</f>
         <v>1180</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="0">
         <f>SUM(R2:R2)</f>
         <v>90</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="0">
         <f>SUM(S2:S2)</f>
         <v>90</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="0">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="0">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>1180</v>
       </c>
-      <c r="AD3" t="s">
-        <v>344</v>
+      <c r="AD3" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -12629,32 +12618,32 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -12746,16 +12735,16 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="0">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:33">
@@ -12763,16 +12752,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -12786,8 +12775,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -12836,29 +12825,29 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="AA2" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>11800</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE2" s="0">
         <v>34</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="AG2" t="s">
-        <v>353</v>
+      <c r="AG2" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -12866,19 +12855,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I3" s="1">
         <v>1000</v>
@@ -12889,8 +12878,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -12939,70 +12928,70 @@
         <v>191</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD3" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE3">
+      <c r="AD3" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE3" s="0">
         <v>34</v>
       </c>
-      <c r="AF3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>353</v>
+      <c r="AF3" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="AG3" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:33">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>11000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
         <v>9000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
         <v>10620</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>11000</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="0">
         <f>SUM(R2:R3)</f>
         <v>990</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="0">
         <f>SUM(S2:S3)</f>
         <v>990</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="0">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="0">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
         <v>10620</v>
       </c>
-      <c r="AD4" t="s">
-        <v>344</v>
+      <c r="AD4" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -13016,32 +13005,32 @@
   <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -13133,16 +13122,16 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="0">
         <v>3</v>
       </c>
       <c r="AF1" s="56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:33">
@@ -13150,19 +13139,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I2" s="1">
         <v>1000</v>
@@ -13173,8 +13162,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -13223,70 +13212,70 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>82500</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE2" s="0">
         <v>34</v>
       </c>
-      <c r="AF2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>353</v>
+      <c r="AF2" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
-      <c r="I3">
+      <c r="I3" s="0">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>1000</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>82500</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="0">
         <f>SUM(R2:R2)</f>
         <v>0</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="0">
         <f>SUM(S2:S2)</f>
         <v>0</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="0">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="0">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>82500</v>
       </c>
-      <c r="AD3" t="s">
-        <v>344</v>
+      <c r="AD3" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -13300,32 +13289,32 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -13417,16 +13406,16 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="0">
         <v>3</v>
       </c>
       <c r="AF1" s="56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:33">
@@ -13434,16 +13423,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -13457,8 +13446,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -13507,29 +13496,29 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="AA2" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>10000</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE2" s="0">
         <v>34</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="AG2" t="s">
-        <v>353</v>
+      <c r="AG2" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -13537,19 +13526,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I3" s="1">
         <v>1000</v>
@@ -13560,8 +13549,8 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s">
-        <v>320</v>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M3" s="38">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
@@ -13610,70 +13599,70 @@
         <v>191</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE3">
+      <c r="AD3" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE3" s="0">
         <v>34</v>
       </c>
-      <c r="AF3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>353</v>
+      <c r="AF3" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="AG3" t="s" s="0">
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:33">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I3)</f>
         <v>11000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>ROUND(M2-M3,2)</f>
         <v>9000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>ROUND(N2-N3,2)</f>
         <v>9000</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>11000</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="0">
         <f>SUM(R2:R3)</f>
         <v>0</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="0">
         <f>SUM(S2:S3)</f>
         <v>0</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="0">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="0">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>ROUND(AC2-AC3,2)</f>
         <v>9000</v>
       </c>
-      <c r="AD4" t="s">
-        <v>344</v>
+      <c r="AD4" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -13687,32 +13676,32 @@
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -13804,22 +13793,22 @@
         <v>309</v>
       </c>
       <c r="AD1" s="37" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AE1" s="1">
         <v>1</v>
       </c>
       <c r="AF1" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG1" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="AH1" s="57" t="s">
         <v>355</v>
       </c>
-      <c r="AG1" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="AH1" s="57" t="s">
-        <v>359</v>
-      </c>
       <c r="AI1" s="57" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:35">
@@ -13827,19 +13816,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I2" s="1">
         <v>1000</v>
@@ -13900,7 +13889,7 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>310</v>
@@ -13913,16 +13902,16 @@
         <v>1180</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AE2" s="1">
         <v>34</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AH2" s="54">
         <v>0.01</v>
@@ -13937,19 +13926,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I3" s="1">
         <f>AI2</f>
@@ -14008,7 +13997,7 @@
         <v>191</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AA3" s="1" t="s">
         <v>310</v>
@@ -14021,7 +14010,7 @@
         <v>10</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -14030,44 +14019,44 @@
       <c r="AI3" s="1"/>
     </row>
     <row r="4" spans="1:35">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2)</f>
         <v>1000</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2)</f>
         <v>1180</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q3)</f>
         <v>1000</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="0">
         <f>SUM(R2:R3)</f>
         <v>90</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="0">
         <f>SUM(S2:S3)</f>
         <v>90</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="0">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="0">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>AC2-AC3</f>
         <v>1170</v>
       </c>
-      <c r="AD4" t="s">
-        <v>344</v>
+      <c r="AD4" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -14081,32 +14070,32 @@
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -14198,22 +14187,22 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="AE1">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="0">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG1" s="55" t="s">
+        <v>351</v>
+      </c>
+      <c r="AH1" s="57" t="s">
         <v>355</v>
       </c>
-      <c r="AG1" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="AH1" s="57" t="s">
-        <v>359</v>
-      </c>
       <c r="AI1" s="57" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:35">
@@ -14221,19 +14210,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I2" s="1">
         <v>1000</v>
@@ -14244,8 +14233,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -14294,29 +14283,29 @@
         <v>191</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="AE2" s="0">
         <v>34</v>
       </c>
-      <c r="AF2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>353</v>
+      <c r="AF2" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>350</v>
       </c>
       <c r="AH2" s="54">
         <v>0.01</v>
@@ -14331,19 +14320,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>349</v>
       </c>
       <c r="I3" s="1">
         <f>AI2</f>
@@ -14402,12 +14391,12 @@
         <v>191</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -14415,7 +14404,7 @@
         <v>10</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -14424,44 +14413,44 @@
       <c r="AI3" s="1"/>
     </row>
     <row r="4" spans="1:35">
-      <c r="I4">
+      <c r="I4" s="0">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <f>SUM(M2+R2+S2+T2+U2+W2)-M3</f>
         <v>1170</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0">
         <f>SUM(N2+R2+S2+T2+U2+W2)-N3</f>
         <v>1170</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="0">
         <f>SUM(R2:R2)</f>
         <v>90</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="0">
         <f>SUM(S2:S2)</f>
         <v>90</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="0">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="0">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="0">
         <f>AC2-AC3</f>
         <v>1170</v>
       </c>
-      <c r="AD4" t="s">
-        <v>344</v>
+      <c r="AD4" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -14475,29 +14464,29 @@
   <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="11" max="11" customWidth="true" width="21.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -14589,7 +14578,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -14597,7 +14586,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>280</v>
@@ -14609,10 +14598,10 @@
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -14626,8 +14615,8 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s">
-        <v>320</v>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -14658,45 +14647,45 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>10000</v>
       </c>
-      <c r="AD2" t="s">
-        <v>344</v>
+      <c r="AD2" t="s" s="0">
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
-      <c r="M3">
+      <c r="M3" s="0">
         <f>SUM(M2)</f>
         <v>10000</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0">
         <f>SUM(N2)</f>
         <v>10000</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <f>SUM(Q2)</f>
         <v>10000</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="0">
         <f>SUM(AC2)</f>
         <v>10000</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -14710,39 +14699,39 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="28.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>50</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>30</v>
       </c>
     </row>
@@ -14756,13 +14745,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="19.7109375"/>
+    <col min="2" max="2" customWidth="true" width="8.140625"/>
+    <col min="3" max="3" customWidth="true" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" width="17.85546875"/>
+    <col min="5" max="5" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="14.5703125"/>
+    <col min="7" max="7" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -14861,13 +14850,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="19.7109375"/>
+    <col min="2" max="2" customWidth="true" width="8.140625"/>
+    <col min="3" max="3" customWidth="true" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" width="17.85546875"/>
+    <col min="5" max="5" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="14.5703125"/>
+    <col min="7" max="7" customWidth="true" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -14966,23 +14955,23 @@
   <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="13" max="14" width="39.7109375" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
-    <col min="16" max="17" width="16.5703125" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="39.7109375"/>
+    <col min="2" max="2" customWidth="true" width="10.140625"/>
+    <col min="3" max="3" customWidth="true" width="39.7109375"/>
+    <col min="4" max="4" customWidth="true" width="11.0"/>
+    <col min="5" max="5" customWidth="true" width="13.28515625"/>
+    <col min="6" max="6" customWidth="true" width="8.85546875"/>
+    <col min="7" max="7" customWidth="true" width="17.85546875"/>
+    <col min="8" max="8" customWidth="true" width="19.5703125"/>
+    <col min="9" max="9" customWidth="true" width="23.7109375"/>
+    <col min="10" max="10" customWidth="true" width="12.7109375"/>
+    <col min="11" max="11" customWidth="true" width="11.85546875"/>
+    <col min="12" max="12" customWidth="true" width="17.42578125"/>
+    <col min="13" max="14" customWidth="true" width="39.7109375"/>
+    <col min="15" max="15" customWidth="true" width="25.7109375"/>
+    <col min="16" max="17" customWidth="true" width="16.5703125"/>
+    <col min="18" max="18" customWidth="true" width="11.5703125"/>
+    <col min="19" max="19" customWidth="true" width="14.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="54" activeTab="54"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="24" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="358">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -1158,14 +1158,13 @@
     <t>TDS AMT</t>
   </si>
   <si>
-    <t>666.3</t>
+    <t>26550</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="23">
     <font>
       <sz val="11"/>
@@ -2089,15 +2088,15 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.7109375"/>
-    <col min="2" max="3" customWidth="true" width="12.7109375"/>
-    <col min="4" max="4" customWidth="true" width="14.7109375"/>
-    <col min="5" max="5" customWidth="true" width="9.85546875"/>
-    <col min="6" max="6" customWidth="true" width="14.140625"/>
-    <col min="7" max="7" customWidth="true" width="14.85546875"/>
-    <col min="8" max="8" customWidth="true" width="22.28515625"/>
-    <col min="9" max="9" customWidth="true" width="14.42578125"/>
-    <col min="10" max="10" customWidth="true" width="13.0"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2430,17 +2429,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="9.0"/>
-    <col min="2" max="2" customWidth="true" width="25.7109375"/>
-    <col min="3" max="3" customWidth="true" width="12.42578125"/>
-    <col min="4" max="4" customWidth="true" width="16.28515625"/>
-    <col min="5" max="5" customWidth="true" width="20.28515625"/>
-    <col min="6" max="6" customWidth="true" width="25.7109375"/>
-    <col min="7" max="7" customWidth="true" width="12.28515625"/>
-    <col min="8" max="8" customWidth="true" width="14.5703125"/>
-    <col min="9" max="9" customWidth="true" width="28.5703125"/>
-    <col min="10" max="10" customWidth="true" width="23.0"/>
-    <col min="11" max="11" customWidth="true" width="14.7109375"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2663,11 +2662,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="13.5703125"/>
-    <col min="2" max="2" customWidth="true" width="6.0"/>
-    <col min="3" max="3" customWidth="true" width="14.42578125"/>
-    <col min="4" max="4" customWidth="true" width="18.140625"/>
-    <col min="5" max="5" customWidth="true" width="19.5703125"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2748,13 +2747,13 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="25.7109375"/>
-    <col min="2" max="2" customWidth="true" width="8.85546875"/>
-    <col min="3" max="3" customWidth="true" width="12.28515625"/>
-    <col min="4" max="4" customWidth="true" width="7.140625"/>
-    <col min="5" max="5" customWidth="true" width="5.28515625"/>
-    <col min="6" max="6" customWidth="true" width="17.42578125"/>
-    <col min="7" max="7" customWidth="true" width="12.42578125"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3089,9 +3088,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="25.5703125"/>
-    <col min="2" max="2" customWidth="true" width="15.140625"/>
-    <col min="3" max="3" customWidth="true" width="16.42578125"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3137,12 +3136,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
-    <col min="2" max="2" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="5" max="5" customWidth="true" width="19.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3175,13 +3174,13 @@
       <c r="C2" s="1">
         <v>10</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>249</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <f>ROUND(C2*E2,2)</f>
         <v>847.48</v>
       </c>
@@ -3196,13 +3195,13 @@
       <c r="C3" s="1">
         <v>12</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>252</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="0">
+      <c r="F3">
         <f>ROUND(C3*E3,2)</f>
         <v>159.26</v>
       </c>
@@ -3217,9 +3216,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="21.42578125"/>
-    <col min="2" max="2" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" customWidth="true" width="9.0"/>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3265,7 +3264,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.42578125"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3440,26 +3439,26 @@
   <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="30.0"/>
-    <col min="2" max="2" customWidth="true" width="36.42578125"/>
-    <col min="3" max="3" customWidth="true" width="6.0"/>
-    <col min="4" max="4" customWidth="true" width="13.7109375"/>
-    <col min="5" max="5" customWidth="true" width="5.28515625"/>
-    <col min="6" max="6" customWidth="true" width="17.28515625"/>
-    <col min="7" max="7" customWidth="true" width="30.28515625"/>
-    <col min="8" max="8" customWidth="true" width="26.85546875"/>
-    <col min="9" max="9" customWidth="true" width="17.28515625"/>
-    <col min="10" max="10" customWidth="true" width="13.28515625"/>
-    <col min="11" max="11" customWidth="true" width="22.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
-    <col min="13" max="13" customWidth="true" width="29.5703125"/>
-    <col min="14" max="14" customWidth="true" width="18.28515625"/>
-    <col min="15" max="15" customWidth="true" width="16.28515625"/>
-    <col min="16" max="16" customWidth="true" width="15.5703125"/>
-    <col min="17" max="17" customWidth="true" width="17.7109375"/>
-    <col min="18" max="18" customWidth="true" width="24.140625"/>
-    <col min="19" max="19" customWidth="true" width="13.42578125"/>
-    <col min="20" max="20" customWidth="true" width="13.5703125"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="29.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3753,7 +3752,7 @@
       <c r="D6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="27" t="s">
@@ -4021,7 +4020,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>234</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -4032,18 +4031,18 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>45</v>
       </c>
     </row>
@@ -4057,25 +4056,25 @@
   <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
-    <col min="3" max="3" customWidth="true" width="22.140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4153,19 +4152,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4174,16 +4173,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>2000</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>276</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>207</v>
       </c>
-      <c r="L2" s="0">
+      <c r="L2">
         <v>1</v>
       </c>
     </row>
@@ -4191,19 +4190,19 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>284</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="F3" t="s">
         <v>274</v>
       </c>
       <c r="G3" s="39" t="s">
@@ -4212,16 +4211,16 @@
       <c r="H3" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I3" s="0">
+      <c r="I3">
         <v>2000</v>
       </c>
-      <c r="J3" t="s" s="0">
+      <c r="J3" t="s">
         <v>276</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="K3" t="s">
         <v>207</v>
       </c>
-      <c r="L3" s="0">
+      <c r="L3">
         <v>1</v>
       </c>
     </row>
@@ -4346,25 +4345,25 @@
   <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
-    <col min="3" max="3" customWidth="true" width="22.140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4442,19 +4441,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4463,16 +4462,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>2000</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>276</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>207</v>
       </c>
-      <c r="L2" s="0">
+      <c r="L2">
         <v>1</v>
       </c>
     </row>
@@ -4545,25 +4544,25 @@
   <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
-    <col min="3" max="3" customWidth="true" width="22.140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="8.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -4641,19 +4640,19 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>274</v>
       </c>
       <c r="G2" s="39" t="s">
@@ -4662,16 +4661,16 @@
       <c r="H2" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>2000</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>276</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>207</v>
       </c>
-      <c r="L2" s="0">
+      <c r="L2">
         <v>1</v>
       </c>
     </row>
@@ -4744,23 +4743,23 @@
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="22.140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="8.28515625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -4884,7 +4883,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4943,27 +4942,27 @@
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="16.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5115,10 +5114,10 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>188</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="Y2" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5133,27 +5132,27 @@
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="16.140625"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5305,10 +5304,10 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>188</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="Y2" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5323,34 +5322,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5476,7 +5475,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -5508,37 +5507,37 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -5554,34 +5553,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5707,7 +5706,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -5739,31 +5738,31 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="AB2" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -5779,34 +5778,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5932,7 +5931,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -5964,13 +5963,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>1000</v>
       </c>
@@ -6009,7 +6008,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -6041,35 +6040,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>2000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>2000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>2000</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>2000</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>2000</v>
       </c>
@@ -6085,17 +6084,17 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="21.0"/>
-    <col min="3" max="3" customWidth="true" width="6.0"/>
-    <col min="4" max="4" customWidth="true" width="12.7109375"/>
-    <col min="5" max="5" customWidth="true" width="19.42578125"/>
-    <col min="6" max="6" customWidth="true" width="15.140625"/>
-    <col min="7" max="7" customWidth="true" width="15.42578125"/>
-    <col min="8" max="8" customWidth="true" width="19.5703125"/>
-    <col min="9" max="9" customWidth="true" width="10.85546875"/>
-    <col min="10" max="10" customWidth="true" width="17.5703125"/>
-    <col min="11" max="11" customWidth="true" width="11.28515625"/>
-    <col min="12" max="12" customWidth="true" width="21.7109375"/>
+    <col min="1" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6234,34 +6233,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6387,7 +6386,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -6419,13 +6418,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -6464,7 +6463,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -6496,35 +6495,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -6540,34 +6539,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6693,7 +6692,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -6725,13 +6724,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -6770,7 +6769,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -6802,35 +6801,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -6846,34 +6845,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6999,7 +6998,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -7031,37 +7030,37 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -7077,29 +7076,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -7228,7 +7227,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>353</v>
       </c>
       <c r="M2" s="38">
@@ -7260,17 +7259,17 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
     </row>
@@ -7300,7 +7299,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -7332,42 +7331,42 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>10</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>10</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>-10</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>-10</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>10</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-10</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7382,29 +7381,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -7533,7 +7532,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -7565,17 +7564,17 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
     </row>
@@ -7605,7 +7604,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -7637,42 +7636,42 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>100</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>100</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>-100</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>-100</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>100</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-100</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7687,34 +7686,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -7840,7 +7839,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -7872,31 +7871,31 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -7912,34 +7911,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -8065,7 +8064,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -8097,13 +8096,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -8142,7 +8141,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -8174,35 +8173,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -8218,34 +8217,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="24.140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -8371,7 +8370,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -8403,13 +8402,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -8448,7 +8447,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -8480,35 +8479,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -8524,34 +8523,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="24.140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -8677,7 +8676,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -8709,13 +8708,13 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>100</v>
       </c>
@@ -8754,7 +8753,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -8786,35 +8785,35 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>200</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>200</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>200</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>200</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>200</v>
       </c>
@@ -8830,9 +8829,9 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="24.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.7109375"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8888,12 +8887,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.140625"/>
-    <col min="2" max="2" customWidth="true" width="10.42578125"/>
-    <col min="3" max="3" customWidth="true" width="11.42578125"/>
-    <col min="4" max="4" customWidth="true" width="11.7109375"/>
-    <col min="5" max="5" customWidth="true" width="14.5703125"/>
-    <col min="6" max="6" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8964,26 +8963,26 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9109,7 +9108,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -9141,25 +9140,25 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM(AA2+AB2),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -9175,28 +9174,28 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9322,7 +9321,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -9354,37 +9353,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2" t="s">
+        <v>357</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -9400,34 +9399,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9553,7 +9552,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -9585,13 +9584,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -9630,7 +9629,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -9654,31 +9653,31 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -9694,34 +9693,34 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -9847,7 +9846,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>312</v>
       </c>
       <c r="M2" s="38">
@@ -9879,37 +9878,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>0</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>0</v>
       </c>
@@ -9925,34 +9924,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="10.42578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10078,7 +10077,7 @@
       <c r="K2" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>312</v>
       </c>
       <c r="M2" s="45">
@@ -10110,13 +10109,13 @@
       <c r="Z2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>283500</v>
       </c>
@@ -10155,7 +10154,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>312</v>
       </c>
       <c r="M3" s="38">
@@ -10187,10 +10186,10 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -10199,31 +10198,31 @@
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>400</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>7000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>567000</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>7000</v>
       </c>
-      <c r="AA4" s="0">
+      <c r="AA4">
         <f>SUM(AA2:AA3)</f>
         <v>0</v>
       </c>
-      <c r="AB4" s="0">
+      <c r="AB4">
         <f>SUM(AB2:AB3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>567000</v>
       </c>
@@ -10239,34 +10238,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="10.42578125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10392,7 +10391,7 @@
       <c r="K2" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>312</v>
       </c>
       <c r="M2" s="45">
@@ -10424,13 +10423,13 @@
       <c r="Z2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
@@ -10469,7 +10468,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>312</v>
       </c>
       <c r="M3" s="38">
@@ -10501,10 +10500,10 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -10513,31 +10512,31 @@
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>0</v>
       </c>
-      <c r="AA4" s="0">
+      <c r="AA4">
         <f>SUM(AA2:AA3)</f>
         <v>0</v>
       </c>
-      <c r="AB4" s="0">
+      <c r="AB4">
         <f>SUM(AB2:AB3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -10553,34 +10552,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -10706,7 +10705,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -10738,13 +10737,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>1000</v>
       </c>
@@ -10783,7 +10782,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -10807,31 +10806,31 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>2000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2:M3)</f>
         <v>2000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2:N3)</f>
         <v>2000</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>2000</v>
       </c>
@@ -10847,34 +10846,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11032,13 +11031,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM(AA2+AB2),2)</f>
         <v>0</v>
       </c>
@@ -11098,19 +11097,19 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM(AA3+AB3),2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>0</v>
       </c>
@@ -11126,34 +11125,34 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11311,13 +11310,13 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
         <v>1000</v>
       </c>
@@ -11377,19 +11376,19 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <f>ROUND(SUM(AA3+AB3+I3),2)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>SUM(AC2:AC3)</f>
         <v>2000</v>
       </c>
@@ -11405,28 +11404,28 @@
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -11552,7 +11551,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -11584,37 +11583,37 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>10000</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>10000</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>10000</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>10000</v>
       </c>
@@ -11630,12 +11629,12 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.140625"/>
-    <col min="2" max="2" customWidth="true" width="10.42578125"/>
-    <col min="3" max="3" customWidth="true" width="11.42578125"/>
-    <col min="4" max="4" customWidth="true" width="11.7109375"/>
-    <col min="5" max="5" customWidth="true" width="14.5703125"/>
-    <col min="6" max="6" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -11724,29 +11723,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -11875,7 +11874,7 @@
       <c r="K2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>312</v>
       </c>
       <c r="M2" s="38">
@@ -11907,17 +11906,17 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
     </row>
@@ -11947,7 +11946,7 @@
       <c r="K3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L3" s="0">
+      <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" s="38">
@@ -11979,42 +11978,42 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>1000</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>342</v>
       </c>
     </row>
@@ -12029,29 +12028,29 @@
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -12180,7 +12179,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -12212,17 +12211,17 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
     </row>
@@ -12252,7 +12251,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -12284,42 +12283,42 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>1000</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>-1000</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>342</v>
       </c>
     </row>
@@ -12334,32 +12333,32 @@
   <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -12453,7 +12452,7 @@
       <c r="AD1" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="AE1" s="0">
+      <c r="AE1">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
@@ -12491,7 +12490,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -12543,67 +12542,67 @@
       <c r="Z2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>34</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>349</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
-      <c r="I3" s="0">
+      <c r="I3">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2+R2+S2+T2+U2+W2)</f>
         <v>1180</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2+R2+S2+T2+U2+W2)</f>
         <v>1180</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R3" s="0">
+      <c r="R3">
         <f>SUM(R2:R2)</f>
         <v>90</v>
       </c>
-      <c r="S3" s="0">
+      <c r="S3">
         <f>SUM(S2:S2)</f>
         <v>90</v>
       </c>
-      <c r="T3" s="0">
+      <c r="T3">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U3" s="0">
+      <c r="U3">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>1180</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>341</v>
       </c>
     </row>
@@ -12618,32 +12617,32 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -12737,7 +12736,7 @@
       <c r="AD1" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="AE1" s="0">
+      <c r="AE1">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
@@ -12775,7 +12774,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -12827,26 +12826,26 @@
       <c r="Z2" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>11800</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>34</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>180</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>350</v>
       </c>
     </row>
@@ -12878,7 +12877,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -12930,67 +12929,67 @@
       <c r="Z3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>341</v>
       </c>
-      <c r="AE3" s="0">
+      <c r="AE3">
         <v>34</v>
       </c>
-      <c r="AF3" t="s" s="0">
+      <c r="AF3" t="s">
         <v>349</v>
       </c>
-      <c r="AG3" t="s" s="0">
+      <c r="AG3" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:33">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>11000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>9000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>10620</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>11000</v>
       </c>
-      <c r="R4" s="0">
+      <c r="R4">
         <f>SUM(R2:R3)</f>
         <v>990</v>
       </c>
-      <c r="S4" s="0">
+      <c r="S4">
         <f>SUM(S2:S3)</f>
         <v>990</v>
       </c>
-      <c r="T4" s="0">
+      <c r="T4">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4" s="0">
+      <c r="U4">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>10620</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>341</v>
       </c>
     </row>
@@ -13005,32 +13004,32 @@
   <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -13124,7 +13123,7 @@
       <c r="AD1" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="AE1" s="0">
+      <c r="AE1">
         <v>3</v>
       </c>
       <c r="AF1" s="56" t="s">
@@ -13162,7 +13161,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -13214,67 +13213,67 @@
       <c r="Z2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>82500</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>34</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>349</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:33">
-      <c r="I3" s="0">
+      <c r="I3">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>1000</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>82500</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R3" s="0">
+      <c r="R3">
         <f>SUM(R2:R2)</f>
         <v>0</v>
       </c>
-      <c r="S3" s="0">
+      <c r="S3">
         <f>SUM(S2:S2)</f>
         <v>0</v>
       </c>
-      <c r="T3" s="0">
+      <c r="T3">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U3" s="0">
+      <c r="U3">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>82500</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>341</v>
       </c>
     </row>
@@ -13289,32 +13288,32 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -13408,7 +13407,7 @@
       <c r="AD1" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="AE1" s="0">
+      <c r="AE1">
         <v>3</v>
       </c>
       <c r="AF1" s="56" t="s">
@@ -13446,7 +13445,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -13498,26 +13497,26 @@
       <c r="Z2" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>10000</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>34</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>180</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>350</v>
       </c>
     </row>
@@ -13549,7 +13548,7 @@
       <c r="K3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>319</v>
       </c>
       <c r="M3" s="38">
@@ -13601,67 +13600,67 @@
       <c r="Z3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
         <v>1000</v>
       </c>
-      <c r="AD3" t="s" s="0">
+      <c r="AD3" t="s">
         <v>341</v>
       </c>
-      <c r="AE3" s="0">
+      <c r="AE3">
         <v>34</v>
       </c>
-      <c r="AF3" t="s" s="0">
+      <c r="AF3" t="s">
         <v>349</v>
       </c>
-      <c r="AG3" t="s" s="0">
+      <c r="AG3" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:33">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I3)</f>
         <v>11000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>ROUND(M2-M3,2)</f>
         <v>9000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>ROUND(N2-N3,2)</f>
         <v>9000</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>11000</v>
       </c>
-      <c r="R4" s="0">
+      <c r="R4">
         <f>SUM(R2:R3)</f>
         <v>0</v>
       </c>
-      <c r="S4" s="0">
+      <c r="S4">
         <f>SUM(S2:S3)</f>
         <v>0</v>
       </c>
-      <c r="T4" s="0">
+      <c r="T4">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4" s="0">
+      <c r="U4">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>ROUND(AC2-AC3,2)</f>
         <v>9000</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>341</v>
       </c>
     </row>
@@ -13676,32 +13675,32 @@
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -14019,43 +14018,43 @@
       <c r="AI3" s="1"/>
     </row>
     <row r="4" spans="1:35">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2)</f>
         <v>1000</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2)</f>
         <v>1180</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q3)</f>
         <v>1000</v>
       </c>
-      <c r="R4" s="0">
+      <c r="R4">
         <f>SUM(R2:R3)</f>
         <v>90</v>
       </c>
-      <c r="S4" s="0">
+      <c r="S4">
         <f>SUM(S2:S3)</f>
         <v>90</v>
       </c>
-      <c r="T4" s="0">
+      <c r="T4">
         <f>SUM(T2:T3)</f>
         <v>0</v>
       </c>
-      <c r="U4" s="0">
+      <c r="U4">
         <f>SUM(U2:U3)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>AC2-AC3</f>
         <v>1170</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>341</v>
       </c>
     </row>
@@ -14070,32 +14069,32 @@
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -14189,7 +14188,7 @@
       <c r="AD1" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="AE1" s="0">
+      <c r="AE1">
         <v>1</v>
       </c>
       <c r="AF1" s="56" t="s">
@@ -14233,7 +14232,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -14285,26 +14284,26 @@
       <c r="Z2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
         <v>1180</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>34</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>349</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>350</v>
       </c>
       <c r="AH2" s="54">
@@ -14393,10 +14392,10 @@
       <c r="Z3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
       <c r="AC3" s="1">
@@ -14413,43 +14412,43 @@
       <c r="AI3" s="1"/>
     </row>
     <row r="4" spans="1:35">
-      <c r="I4" s="0">
+      <c r="I4">
         <f>SUM(I2:I2)</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4">
         <f>SUM(M2+R2+S2+T2+U2+W2)-M3</f>
         <v>1170</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4">
         <f>SUM(N2+R2+S2+T2+U2+W2)-N3</f>
         <v>1170</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="Q4">
         <f>SUM(Q2:Q2)</f>
         <v>1000</v>
       </c>
-      <c r="R4" s="0">
+      <c r="R4">
         <f>SUM(R2:R2)</f>
         <v>90</v>
       </c>
-      <c r="S4" s="0">
+      <c r="S4">
         <f>SUM(S2:S2)</f>
         <v>90</v>
       </c>
-      <c r="T4" s="0">
+      <c r="T4">
         <f>SUM(T2:T2)</f>
         <v>0</v>
       </c>
-      <c r="U4" s="0">
+      <c r="U4">
         <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="0">
+      <c r="AC4">
         <f>AC2-AC3</f>
         <v>1170</v>
       </c>
-      <c r="AD4" t="s" s="0">
+      <c r="AD4" t="s">
         <v>341</v>
       </c>
     </row>
@@ -14464,29 +14463,29 @@
   <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -14615,7 +14614,7 @@
       <c r="K2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>319</v>
       </c>
       <c r="M2" s="38">
@@ -14647,40 +14646,40 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>310</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>310</v>
       </c>
-      <c r="AC2" s="0">
+      <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
         <v>10000</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:30">
-      <c r="M3" s="0">
+      <c r="M3">
         <f>SUM(M2)</f>
         <v>10000</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <f>SUM(N2)</f>
         <v>10000</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="Q3">
         <f>SUM(Q2)</f>
         <v>10000</v>
       </c>
-      <c r="AA3" t="s" s="0">
+      <c r="AA3" t="s">
         <v>310</v>
       </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AB3" t="s">
         <v>310</v>
       </c>
-      <c r="AC3" s="0">
+      <c r="AC3">
         <f>SUM(AC2)</f>
         <v>10000</v>
       </c>
@@ -14699,39 +14698,39 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="28.7109375"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>100</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>50</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>30</v>
       </c>
     </row>
@@ -14745,13 +14744,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="19.7109375"/>
-    <col min="2" max="2" customWidth="true" width="8.140625"/>
-    <col min="3" max="3" customWidth="true" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" width="17.85546875"/>
-    <col min="5" max="5" customWidth="true" width="12.7109375"/>
-    <col min="6" max="6" customWidth="true" width="14.5703125"/>
-    <col min="7" max="7" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -14850,13 +14849,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="19.7109375"/>
-    <col min="2" max="2" customWidth="true" width="8.140625"/>
-    <col min="3" max="3" customWidth="true" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" width="17.85546875"/>
-    <col min="5" max="5" customWidth="true" width="12.7109375"/>
-    <col min="6" max="6" customWidth="true" width="14.5703125"/>
-    <col min="7" max="7" customWidth="true" width="17.7109375"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -14955,23 +14954,23 @@
   <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="39.7109375"/>
-    <col min="2" max="2" customWidth="true" width="10.140625"/>
-    <col min="3" max="3" customWidth="true" width="39.7109375"/>
-    <col min="4" max="4" customWidth="true" width="11.0"/>
-    <col min="5" max="5" customWidth="true" width="13.28515625"/>
-    <col min="6" max="6" customWidth="true" width="8.85546875"/>
-    <col min="7" max="7" customWidth="true" width="17.85546875"/>
-    <col min="8" max="8" customWidth="true" width="19.5703125"/>
-    <col min="9" max="9" customWidth="true" width="23.7109375"/>
-    <col min="10" max="10" customWidth="true" width="12.7109375"/>
-    <col min="11" max="11" customWidth="true" width="11.85546875"/>
-    <col min="12" max="12" customWidth="true" width="17.42578125"/>
-    <col min="13" max="14" customWidth="true" width="39.7109375"/>
-    <col min="15" max="15" customWidth="true" width="25.7109375"/>
-    <col min="16" max="17" customWidth="true" width="16.5703125"/>
-    <col min="18" max="18" customWidth="true" width="11.5703125"/>
-    <col min="19" max="19" customWidth="true" width="14.85546875"/>
+    <col min="1" max="1" width="39.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="13" max="14" width="39.7109375" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" customWidth="1"/>
+    <col min="16" max="17" width="16.5703125" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="24" activeTab="26"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="53" activeTab="57"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="357">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -1156,9 +1156,6 @@
   </si>
   <si>
     <t>TDS AMT</t>
-  </si>
-  <si>
-    <t>26550</t>
   </si>
 </sst>
 </file>
@@ -5738,11 +5735,11 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
+      <c r="AA2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>310</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -6418,11 +6415,11 @@
       <c r="Z2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
+      <c r="AA2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>310</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -6495,11 +6492,11 @@
       <c r="Z3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
+      <c r="AA3" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>310</v>
       </c>
       <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -9354,10 +9351,10 @@
         <v>276</v>
       </c>
       <c r="AA2" t="s">
-        <v>357</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>310</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -9584,11 +9581,11 @@
       <c r="Z2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
+      <c r="AA2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>310</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -9653,11 +9650,11 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
+      <c r="AA3" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>310</v>
       </c>
       <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -10423,11 +10420,11 @@
       <c r="Z2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>310</v>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -10500,11 +10497,11 @@
       <c r="Z3" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA3" t="s">
-        <v>310</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>310</v>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
       </c>
       <c r="AC3" s="1">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="31" activeTab="33"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="85" activeTab="87"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -86,16 +86,16 @@
     <sheet name="TDS CPJournalADV" sheetId="125" r:id="rId77"/>
     <sheet name="CPJournalADV" sheetId="123" r:id="rId78"/>
     <sheet name="TDS CPAdvance" sheetId="124" r:id="rId79"/>
-    <sheet name="TDS CPJournalADVWithNewRef" sheetId="134" r:id="rId80"/>
-    <sheet name="TDS CPAdvanceWithNewRef" sheetId="133" r:id="rId81"/>
+    <sheet name="TDS CPAdvanceWithNewRef" sheetId="133" r:id="rId80"/>
+    <sheet name="TDS CPJournalADVWithNewRef" sheetId="134" r:id="rId81"/>
     <sheet name="TDS CPAdvanceMultiNewRef" sheetId="135" r:id="rId82"/>
     <sheet name="TDS CPJournalADVMultiNewref" sheetId="136" r:id="rId83"/>
     <sheet name="TDS CPAdvanceMulti" sheetId="130" r:id="rId84"/>
     <sheet name="TDS CPJournalADVMulti" sheetId="129" r:id="rId85"/>
     <sheet name="CPAdvanceMulti" sheetId="127" r:id="rId86"/>
     <sheet name="CPAdvanceWithNewRef" sheetId="132" r:id="rId87"/>
-    <sheet name="CPAdvance" sheetId="122" r:id="rId88"/>
-    <sheet name="CPJournalADVWithNewRef" sheetId="131" r:id="rId89"/>
+    <sheet name="CPJournalADVWithNewRef" sheetId="131" r:id="rId88"/>
+    <sheet name="CPAdvance" sheetId="122" r:id="rId89"/>
     <sheet name="BPJournalADVWithNewRef" sheetId="145" r:id="rId90"/>
     <sheet name="TDS BPJournalADVMultiNewref" sheetId="148" r:id="rId91"/>
     <sheet name="TDS BPJournalADVWithNewRef" sheetId="147" r:id="rId92"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5523" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5487" uniqueCount="430">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -1321,9 +1321,6 @@
     <t>Purchase Order 2</t>
   </si>
   <si>
-    <t>CPC-10001</t>
-  </si>
-  <si>
     <t>194C</t>
   </si>
   <si>
@@ -1378,9 +1375,6 @@
     <t>Charges</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
@@ -1475,6 +1469,9 @@
   </si>
   <si>
     <t>UNRELIZED GAIN/LOSS</t>
+  </si>
+  <si>
+    <t>1000</t>
   </si>
 </sst>
 </file>
@@ -1482,19 +1479,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1824,21 +1814,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1847,25 +1837,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1877,10 +1867,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1890,86 +1880,83 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1978,31 +1965,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -2011,25 +2001,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -2041,10 +2028,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -2071,7 +2058,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7500,7 +7487,7 @@
         <v>309</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -7956,7 +7943,7 @@
       </c>
       <c r="I2" s="47">
         <f>ROUND(SUM(ROUND(G2,2)+ROUND(H2,2))*K1,2)</f>
-        <v>11000</v>
+        <v>8500</v>
       </c>
       <c r="J2" s="59">
         <v>0</v>
@@ -8006,7 +7993,7 @@
       </c>
       <c r="J3" s="59">
         <f>ROUND(SUM(ROUND(G3,2)+ROUND(H3,2))*K1,2)</f>
-        <v>11000</v>
+        <v>8500</v>
       </c>
     </row>
   </sheetData>
@@ -14195,14 +14182,14 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="75" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>281</v>
@@ -14210,7 +14197,7 @@
       <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="74" t="s">
         <v>339</v>
       </c>
       <c r="H2" s="22" t="s">
@@ -14441,7 +14428,7 @@
       <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="74" t="s">
         <v>339</v>
       </c>
       <c r="H2" s="22" t="s">
@@ -14820,19 +14807,19 @@
         <v>329</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="AF1" s="64" t="s">
+      <c r="AG1" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="AG1" s="64" t="s">
+      <c r="AH1" s="64" t="s">
         <v>392</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -14912,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AE2" s="0">
         <v>1000000029</v>
@@ -14933,12 +14920,12 @@
       <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>349</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E3" s="24"/>
       <c r="F3" s="1" t="s">
@@ -14947,12 +14934,12 @@
       <c r="G3" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="66"/>
+      <c r="H3" s="65"/>
       <c r="I3" s="24"/>
       <c r="J3" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="K3" s="69" t="s">
+      <c r="K3" s="68" t="s">
         <v>207</v>
       </c>
       <c r="L3" t="s" s="0">
@@ -15160,7 +15147,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C3" s="1">
@@ -15187,8 +15174,8 @@
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
@@ -15366,19 +15353,19 @@
         <v>309</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="AF1" s="64" t="s">
+      <c r="AG1" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="AG1" s="64" t="s">
+      <c r="AH1" s="64" t="s">
         <v>392</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -15395,7 +15382,7 @@
         <v>375</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>316</v>
@@ -15458,7 +15445,7 @@
         <v>221.25</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AE2" s="0">
         <v>1000000029</v>
@@ -15479,22 +15466,22 @@
       <c r="A3" s="41">
         <v>2</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="D3" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="E3" s="41" t="s">
         <v>384</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>385</v>
       </c>
       <c r="F3" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="71" t="s">
         <v>339</v>
       </c>
       <c r="H3" s="44" t="s">
@@ -15552,7 +15539,7 @@
         <v>221.25</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AE3" s="0">
         <v>1000000047</v>
@@ -15577,7 +15564,7 @@
         <v>349</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>349</v>
@@ -15666,14 +15653,14 @@
       <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="72" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="73" t="s">
         <v>388</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>389</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="14" t="s">
@@ -15975,7 +15962,7 @@
         <v>2000000100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -16014,7 +16001,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="1">
@@ -16041,8 +16028,8 @@
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -16060,14 +16047,14 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1000000047</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -16087,8 +16074,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -16398,7 +16385,7 @@
         <v>2000000118</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -16522,10 +16509,10 @@
         <v>255</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F1" s="56" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G1" s="37" t="s">
         <v>256</v>
@@ -16591,45 +16578,45 @@
         <v>306</v>
       </c>
       <c r="AB1" s="64" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC1" s="64" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD1" s="64" t="s">
         <v>409</v>
       </c>
-      <c r="AC1" s="64" t="s">
+      <c r="AE1" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="AD1" s="64" t="s">
+      <c r="AF1" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="AG1" s="64" t="s">
+        <v>414</v>
+      </c>
+      <c r="AH1" s="64" t="s">
         <v>411</v>
       </c>
-      <c r="AE1" s="64" t="s">
+      <c r="AI1" s="64" t="s">
         <v>412</v>
-      </c>
-      <c r="AF1" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AG1" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AI1" s="64" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="77" t="s">
-        <v>407</v>
+      <c r="B2" s="76" t="s">
+        <v>405</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>281</v>
@@ -16685,16 +16672,16 @@
         <v>303</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AC2" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AE2" t="s" s="0">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AF2" s="0">
         <f>ROUND(AD2-AB2,2)</f>
@@ -16717,17 +16704,17 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="77" t="s">
-        <v>408</v>
+      <c r="B3" s="76" t="s">
+        <v>406</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>281</v>
@@ -16783,16 +16770,16 @@
         <v>303</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AC3" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AE3" t="s" s="0">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AF3" s="0">
         <f>ROUND(AD3-AB3,2)</f>
@@ -16921,10 +16908,10 @@
         <v>255</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F1" s="56" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G1" s="37" t="s">
         <v>256</v>
@@ -16990,45 +16977,45 @@
         <v>306</v>
       </c>
       <c r="AB1" s="64" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC1" s="64" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD1" s="64" t="s">
         <v>409</v>
       </c>
-      <c r="AC1" s="64" t="s">
+      <c r="AE1" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="AD1" s="64" t="s">
+      <c r="AF1" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="AG1" s="64" t="s">
+        <v>414</v>
+      </c>
+      <c r="AH1" s="64" t="s">
         <v>411</v>
       </c>
-      <c r="AE1" s="64" t="s">
+      <c r="AI1" s="64" t="s">
         <v>412</v>
-      </c>
-      <c r="AF1" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AG1" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AI1" s="64" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="75" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>281</v>
@@ -17084,16 +17071,16 @@
         <v>303</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AC2" t="s" s="0">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AE2" t="s" s="0">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AF2" s="0">
         <f>ROUND(AD2-AB2,2)</f>
@@ -17116,17 +17103,17 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="78" t="s">
-        <v>423</v>
+      <c r="B3" s="77" t="s">
+        <v>421</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>281</v>
@@ -17182,16 +17169,16 @@
         <v>303</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AC3" t="s" s="0">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AE3" t="s" s="0">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AF3" s="0">
         <f>ROUND(AD3-AB3,2)</f>
@@ -19501,7 +19488,7 @@
       <c r="J2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="78" t="s">
         <v>209</v>
       </c>
       <c r="L2" t="s" s="0">
@@ -19763,7 +19750,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AB2" t="s" s="0">
         <v>310</v>
@@ -19777,14 +19764,14 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="79" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>426</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>427</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>428</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -19843,7 +19830,7 @@
         <v>310</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -20070,10 +20057,10 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -20084,14 +20071,14 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="79" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>426</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>427</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>428</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -20147,10 +20134,10 @@
         <v>303</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -20541,14 +20528,14 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="79" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>426</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>427</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>428</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -20783,8 +20770,8 @@
       <c r="C3" s="1">
         <v>2000000124</v>
       </c>
-      <c r="D3" s="80" t="s">
-        <v>426</v>
+      <c r="D3" s="79" t="s">
+        <v>424</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -20959,8 +20946,8 @@
       <c r="C3" s="1">
         <v>2000000124</v>
       </c>
-      <c r="D3" s="80" t="s">
-        <v>426</v>
+      <c r="D3" s="79" t="s">
+        <v>424</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -21162,8 +21149,8 @@
       <c r="C3" s="1">
         <v>2000000124</v>
       </c>
-      <c r="D3" s="80" t="s">
-        <v>426</v>
+      <c r="D3" s="79" t="s">
+        <v>424</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -21701,7 +21688,7 @@
         <v>5050606001</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -21712,7 +21699,7 @@
       <c r="H4" s="0">
         <v>0</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="80">
         <v>0</v>
       </c>
       <c r="J4" s="59">
@@ -30916,7 +30903,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>310</v>
@@ -31339,7 +31326,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C3" s="1">
@@ -31366,8 +31353,8 @@
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
@@ -31516,7 +31503,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s" s="0">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>310</v>
@@ -31562,7 +31549,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" t="s" s="0">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>310</v>
@@ -31583,7 +31570,7 @@
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
@@ -31614,9 +31601,13 @@
     <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
     <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
     <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="31" max="31" customWidth="true" width="16.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="23.140625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="16.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:34">
       <c r="A1" s="37" t="s">
         <v>253</v>
       </c>
@@ -31704,8 +31695,23 @@
       <c r="AC1" s="40" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
+        <v>390</v>
+      </c>
+      <c r="AG1" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="AH1" s="64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -31724,8 +31730,8 @@
       <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="65" t="s">
-        <v>379</v>
+      <c r="G2" s="24" t="s">
+        <v>339</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -31744,16 +31750,17 @@
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
-        <v>0</v>
+        <f>AC2</f>
+        <v>221.25</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -31778,19 +31785,36 @@
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
+        <v>221.25</v>
+      </c>
+      <c r="AD2" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="AE2" s="0">
+        <v>1000000029</v>
+      </c>
+      <c r="AF2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="0">
+        <f>AC2</f>
+        <v>221.25</v>
+      </c>
+      <c r="AH2" s="0">
+        <f>ROUND(AC2*AF2%,2)</f>
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>349</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E3" s="24"/>
       <c r="F3" s="1" t="s">
@@ -31799,12 +31823,12 @@
       <c r="G3" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="66"/>
+      <c r="H3" s="65"/>
       <c r="I3" s="24"/>
       <c r="J3" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="K3" s="69" t="s">
+      <c r="K3" s="68" t="s">
         <v>207</v>
       </c>
       <c r="L3" t="s" s="0">
@@ -31812,11 +31836,11 @@
       </c>
       <c r="M3" s="38">
         <f>AC3</f>
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="N3" s="38">
         <f>AC3</f>
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -31846,21 +31870,30 @@
       </c>
       <c r="AC3" s="0">
         <f>ROUND(AA2*1%,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>2.21</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
       <c r="M4" s="0">
         <f>SUM(M2)</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="N4" s="0">
         <f>SUM(N2)</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="Q4" s="0">
         <f>SUM(Q2)</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>310</v>
@@ -31870,7 +31903,7 @@
       </c>
       <c r="AC4" s="0">
         <f>SUM(AC2)</f>
-        <v>0</v>
+        <v>221.25</v>
       </c>
     </row>
   </sheetData>
@@ -31986,217 +32019,6 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="8" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="10" max="10" customWidth="true" width="17.42578125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>352</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>353</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>354</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>355</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2000000099</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I2" s="47">
-        <f>ROUND(SUM(G2+H2),2)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="59">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1000000029</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="H3" s="0">
-        <v>0</v>
-      </c>
-      <c r="I3" s="47">
-        <v>0</v>
-      </c>
-      <c r="J3" s="59">
-        <f>ROUND(I2*1%,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1000000028</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I4" s="59">
-        <v>0</v>
-      </c>
-      <c r="J4" s="59">
-        <f>ROUND(I2-J3,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="9" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AH4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -32324,19 +32146,19 @@
         <v>329</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="AF1" s="64" t="s">
+      <c r="AG1" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="AG1" s="64" t="s">
+      <c r="AH1" s="64" t="s">
         <v>392</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -32416,7 +32238,7 @@
         <v>1000</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AE2" s="0">
         <v>1000000029</v>
@@ -32441,7 +32263,7 @@
         <v>349</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>349</v>
@@ -32453,12 +32275,12 @@
       <c r="G3" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="66"/>
+      <c r="H3" s="65"/>
       <c r="I3" s="24"/>
       <c r="J3" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="K3" s="69" t="s">
+      <c r="K3" s="68" t="s">
         <v>207</v>
       </c>
       <c r="L3" t="s" s="0">
@@ -32550,6 +32372,217 @@
         <v>990</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AE9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="8" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="10" max="10" customWidth="true" width="17.42578125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31">
+      <c r="A1" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>355</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2000000099</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="I2" s="47">
+        <f>ROUND(SUM(G2+H2),2)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="59">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1000000029</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0</v>
+      </c>
+      <c r="I3" s="47">
+        <v>0</v>
+      </c>
+      <c r="J3" s="59">
+        <f>ROUND(I2*1%,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1000000028</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="I4" s="59">
+        <v>0</v>
+      </c>
+      <c r="J4" s="59">
+        <f>ROUND(I2-J3,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="9" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32684,19 +32717,19 @@
         <v>309</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="AF1" s="64" t="s">
+      <c r="AG1" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="AG1" s="64" t="s">
+      <c r="AH1" s="64" t="s">
         <v>392</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -32713,7 +32746,7 @@
         <v>375</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>316</v>
@@ -32776,7 +32809,7 @@
         <v>10000</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AE2" s="0">
         <v>1000000029</v>
@@ -32797,26 +32830,26 @@
       <c r="A3" s="41">
         <v>2</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="D3" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="E3" s="41" t="s">
         <v>384</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>385</v>
       </c>
       <c r="F3" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="71" t="s">
         <v>339</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I3" s="41">
         <v>10000</v>
@@ -32870,7 +32903,7 @@
         <v>10000</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AE3" s="0">
         <v>1000000047</v>
@@ -32895,7 +32928,7 @@
         <v>349</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>349</v>
@@ -32908,7 +32941,7 @@
         <v>339</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -32984,14 +33017,14 @@
       <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="72" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="73" t="s">
         <v>388</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>389</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="14" t="s">
@@ -33001,7 +33034,7 @@
         <v>339</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -33203,7 +33236,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s" s="0">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>310</v>
@@ -33244,12 +33277,12 @@
         <v>2000000100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" t="s" s="0">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>310</v>
@@ -33283,7 +33316,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="1">
@@ -33310,8 +33343,8 @@
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -33329,14 +33362,14 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1000000047</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -33356,8 +33389,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -33535,19 +33568,19 @@
         <v>309</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AE1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="AF1" s="64" t="s">
+      <c r="AG1" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="AG1" s="64" t="s">
+      <c r="AH1" s="64" t="s">
         <v>392</v>
-      </c>
-      <c r="AH1" s="64" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -33564,7 +33597,7 @@
         <v>375</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>316</v>
@@ -33627,7 +33660,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AE2" s="0">
         <v>1000000029</v>
@@ -33648,22 +33681,22 @@
       <c r="A3" s="41">
         <v>2</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="D3" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="E3" s="41" t="s">
         <v>384</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>385</v>
       </c>
       <c r="F3" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="71" t="s">
         <v>339</v>
       </c>
       <c r="H3" s="44" t="s">
@@ -33721,7 +33754,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AE3" s="0">
         <v>1000000047</v>
@@ -33746,7 +33779,7 @@
         <v>349</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>349</v>
@@ -33835,14 +33868,14 @@
       <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="72" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="73" t="s">
         <v>388</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>389</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="14" t="s">
@@ -34095,7 +34128,7 @@
         <v>2000000100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -34134,7 +34167,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="1">
@@ -34161,8 +34194,8 @@
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -34180,14 +34213,14 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1000000047</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -34207,8 +34240,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -34396,7 +34429,7 @@
         <v>375</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>316</v>
@@ -34449,7 +34482,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AB2" t="s" s="0">
         <v>310</v>
@@ -34464,16 +34497,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="63" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>316</v>
@@ -34526,7 +34559,7 @@
         <v>303</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AB3" s="0">
         <v>0</v>
@@ -34688,7 +34721,7 @@
         <v>329</v>
       </c>
       <c r="AD1" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -34768,7 +34801,7 @@
         <v>1000</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -34802,6 +34835,170 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AE3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="8" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="10" max="10" customWidth="true" width="17.42578125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31">
+      <c r="A1" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>355</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2000000099</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0</v>
+      </c>
+      <c r="I2" s="47">
+        <f>ROUND(SUM(G2+H2),2)</f>
+        <v>1000</v>
+      </c>
+      <c r="J2" s="59">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1000000028</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0</v>
+      </c>
+      <c r="I3" s="59">
+        <v>0</v>
+      </c>
+      <c r="J3" s="59">
+        <f>ROUND(SUM(G3+H3),2)</f>
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -34944,8 +35141,8 @@
       <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="65" t="s">
-        <v>379</v>
+      <c r="G2" s="47" t="s">
+        <v>339</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>275</v>
@@ -34992,7 +35189,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="AB2" t="s" s="0">
         <v>310</v>
@@ -35023,170 +35220,6 @@
       </c>
       <c r="AC3" s="0">
         <f>SUM(AC2)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="8" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="10" max="10" customWidth="true" width="17.42578125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>352</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>353</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>354</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>355</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2000000099</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I2" s="47">
-        <f>ROUND(SUM(G2+H2),2)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="59">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1000000028</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I3" s="59">
-        <v>0</v>
-      </c>
-      <c r="J3" s="59">
-        <f>ROUND(SUM(G3+H3),2)</f>
         <v>0</v>
       </c>
     </row>
@@ -36443,7 +36476,7 @@
         <v>2000000100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -36482,7 +36515,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="1">
@@ -36509,8 +36542,8 @@
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -36528,14 +36561,14 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1000000047</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -36555,8 +36588,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -36739,7 +36772,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="69" t="s">
         <v>191</v>
       </c>
       <c r="C3" s="1">
@@ -36766,8 +36799,8 @@
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="85" activeTab="87"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="123" activeTab="123"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5487" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5496" uniqueCount="429">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -1375,9 +1375,6 @@
     <t>Charges</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>MAERSK SEALAND(AP)</t>
   </si>
   <si>
@@ -1471,7 +1468,7 @@
     <t>UNRELIZED GAIN/LOSS</t>
   </si>
   <si>
-    <t>1000</t>
+    <t>26550</t>
   </si>
 </sst>
 </file>
@@ -3224,8 +3221,8 @@
       <c r="G2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="H2" s="0">
-        <v>0</v>
+      <c r="H2" t="s" s="0">
+        <v>310</v>
       </c>
       <c r="I2" s="47">
         <f>ROUND(SUM(G2+H2),2)</f>
@@ -3270,8 +3267,8 @@
       <c r="G3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="H3" s="0">
-        <v>0</v>
+      <c r="H3" t="s" s="0">
+        <v>310</v>
       </c>
       <c r="I3" s="59">
         <v>0</v>
@@ -8330,7 +8327,7 @@
       </c>
       <c r="N2" s="38">
         <f>AC2</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -8361,7 +8358,7 @@
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8371,7 +8368,7 @@
       </c>
       <c r="N3" s="0">
         <f>SUM(N2)</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="0">
         <f>SUM(Q2)</f>
@@ -8385,7 +8382,7 @@
       </c>
       <c r="AC3" s="0">
         <f>SUM(AC2)</f>
-        <v>26550</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8586,10 +8583,10 @@
         <v>276</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>310</v>
+        <v>428</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>310</v>
+        <v>428</v>
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -8655,10 +8652,10 @@
         <v>276</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>310</v>
+        <v>428</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>310</v>
+        <v>428</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -14183,13 +14180,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="75" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>281</v>
@@ -16385,7 +16382,7 @@
         <v>2000000118</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -16509,10 +16506,10 @@
         <v>255</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F1" s="56" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G1" s="37" t="s">
         <v>256</v>
@@ -16578,28 +16575,28 @@
         <v>306</v>
       </c>
       <c r="AB1" s="64" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC1" s="64" t="s">
         <v>407</v>
       </c>
-      <c r="AC1" s="64" t="s">
+      <c r="AD1" s="64" t="s">
         <v>408</v>
       </c>
-      <c r="AD1" s="64" t="s">
+      <c r="AE1" s="64" t="s">
         <v>409</v>
       </c>
-      <c r="AE1" s="64" t="s">
+      <c r="AF1" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="AG1" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="AH1" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="AF1" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AG1" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AH1" s="64" t="s">
+      <c r="AI1" s="64" t="s">
         <v>411</v>
-      </c>
-      <c r="AI1" s="64" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:35">
@@ -16607,13 +16604,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>384</v>
@@ -16678,10 +16675,10 @@
         <v>380</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AE2" t="s" s="0">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF2" s="0">
         <f>ROUND(AD2-AB2,2)</f>
@@ -16705,13 +16702,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>384</v>
@@ -16776,10 +16773,10 @@
         <v>380</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AE3" t="s" s="0">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF3" s="0">
         <f>ROUND(AD3-AB3,2)</f>
@@ -16908,10 +16905,10 @@
         <v>255</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F1" s="56" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G1" s="37" t="s">
         <v>256</v>
@@ -16977,28 +16974,28 @@
         <v>306</v>
       </c>
       <c r="AB1" s="64" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC1" s="64" t="s">
         <v>407</v>
       </c>
-      <c r="AC1" s="64" t="s">
+      <c r="AD1" s="64" t="s">
         <v>408</v>
       </c>
-      <c r="AD1" s="64" t="s">
+      <c r="AE1" s="64" t="s">
         <v>409</v>
       </c>
-      <c r="AE1" s="64" t="s">
+      <c r="AF1" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="AG1" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="AH1" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="AF1" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AG1" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AH1" s="64" t="s">
+      <c r="AI1" s="64" t="s">
         <v>411</v>
-      </c>
-      <c r="AI1" s="64" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:35">
@@ -17006,16 +17003,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="75" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>281</v>
@@ -17071,16 +17068,16 @@
         <v>303</v>
       </c>
       <c r="AB2" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="AC2" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="AD2" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AE2" t="s" s="0">
         <v>422</v>
-      </c>
-      <c r="AD2" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="AE2" t="s" s="0">
-        <v>423</v>
       </c>
       <c r="AF2" s="0">
         <f>ROUND(AD2-AB2,2)</f>
@@ -17104,16 +17101,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>281</v>
@@ -17169,16 +17166,16 @@
         <v>303</v>
       </c>
       <c r="AB3" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="AC3" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="AD3" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="AC3" t="s" s="0">
+      <c r="AE3" t="s" s="0">
         <v>422</v>
-      </c>
-      <c r="AD3" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="AE3" t="s" s="0">
-        <v>423</v>
       </c>
       <c r="AF3" s="0">
         <f>ROUND(AD3-AB3,2)</f>
@@ -19750,7 +19747,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AB2" t="s" s="0">
         <v>310</v>
@@ -19765,13 +19762,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="79" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>425</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>426</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -19830,7 +19827,7 @@
         <v>310</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -20057,10 +20054,10 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -20072,13 +20069,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="79" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>425</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>426</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -20134,10 +20131,10 @@
         <v>303</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -20529,13 +20526,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="79" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>425</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>426</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>334</v>
@@ -20771,7 +20768,7 @@
         <v>2000000124</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -20947,7 +20944,7 @@
         <v>2000000124</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -21150,7 +21147,7 @@
         <v>2000000124</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -21688,7 +21685,7 @@
         <v>5050606001</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -30903,7 +30900,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s" s="0">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>310</v>

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="123" activeTab="123"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="136" activeTab="137"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -144,11 +144,11 @@
     <sheet name="BankPaymentChargesINR" sheetId="112" r:id="rId135"/>
     <sheet name="BankPaymentCharges" sheetId="65" r:id="rId136"/>
     <sheet name="BankPaymentExpGST" sheetId="63" r:id="rId137"/>
-    <sheet name="BankPaymentExpUSD" sheetId="103" r:id="rId138"/>
-    <sheet name="BankPaymentExp" sheetId="62" r:id="rId139"/>
-    <sheet name="BankReceiptRevExp" sheetId="58" r:id="rId140"/>
-    <sheet name="BankPaymentExpTDS" sheetId="66" r:id="rId141"/>
-    <sheet name="BankPaymentExpGSTTDS" sheetId="67" r:id="rId142"/>
+    <sheet name="BankPaymentExpGSTTDS" sheetId="67" r:id="rId138"/>
+    <sheet name="BankPaymentExpUSD" sheetId="103" r:id="rId139"/>
+    <sheet name="BankPaymentExp" sheetId="62" r:id="rId140"/>
+    <sheet name="BankReceiptRevExp" sheetId="58" r:id="rId141"/>
+    <sheet name="BankPaymentExpTDS" sheetId="66" r:id="rId142"/>
     <sheet name="BankPaymentPDC" sheetId="61" r:id="rId143"/>
     <sheet name="BPAdvanceUSD" sheetId="161" r:id="rId144"/>
     <sheet name="BPAdvance" sheetId="154" r:id="rId145"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5496" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5626" uniqueCount="429">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -11988,6 +11988,435 @@
 
 <file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet108"/>
+  <dimension ref="A1:AL4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.28515625"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="5.140625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="23.140625"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="17.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38">
+      <c r="A1" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="O1" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="P1" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="R1" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="S1" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="T1" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="V1" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="W1" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="X1" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y1" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA1" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB1" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC1" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD1" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="AE1" s="0">
+        <v>1</v>
+      </c>
+      <c r="AF1" s="55" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG1" s="54" t="s">
+        <v>347</v>
+      </c>
+      <c r="AH1" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="AI1" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="AJ1" s="64" t="s">
+        <v>390</v>
+      </c>
+      <c r="AK1" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="AL1" s="64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="M2" s="38">
+        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
+        <v>1000</v>
+      </c>
+      <c r="N2" s="38">
+        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
+        <v>1000</v>
+      </c>
+      <c r="O2" s="1">
+        <v>88363222</v>
+      </c>
+      <c r="P2" s="53">
+        <v>0.18</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>M2</f>
+        <v>1000</v>
+      </c>
+      <c r="R2" s="1">
+        <f>IF(OR($AE$1=1,$AE$1=4),ROUND((Q2*P2)/2,2),0)</f>
+        <v>90</v>
+      </c>
+      <c r="S2" s="1">
+        <f>IF($AE$1=1,ROUND(((Q2*P2)/2),2),0)</f>
+        <v>90</v>
+      </c>
+      <c r="T2" s="1">
+        <f>IF($AE$1=2,ROUND(((Q2*P2)),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <f>IF($AE$1=4,ROUND(((Q2*P2)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AC2" s="0">
+        <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
+        <v>1180</v>
+      </c>
+      <c r="AD2" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="AE2" s="0">
+        <v>34</v>
+      </c>
+      <c r="AF2" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="AH2" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="AI2" s="0">
+        <v>1000000029</v>
+      </c>
+      <c r="AJ2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="0">
+        <f>I2</f>
+        <v>1000</v>
+      </c>
+      <c r="AL2" s="0">
+        <f>ROUND(M2*AJ2%,2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="I3" s="1">
+        <f>AK2</f>
+        <v>1000</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
+      <c r="M3" s="38">
+        <f>M2*1%</f>
+        <v>10</v>
+      </c>
+      <c r="N3" s="38">
+        <f>M2*1%</f>
+        <v>10</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="53">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <f>IF(OR($AE$1=1,$AE$1=4),ROUND((Q3*P3)/2,2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <f>IF($AE$1=1,ROUND(((Q3*P3)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <f>IF($AE$1=2,ROUND(((Q3*P3)),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <f>IF($AE$1=4,ROUND(((Q3*P3)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AB3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AC3" s="1">
+        <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
+        <v>1000</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="I4" s="0">
+        <f>SUM(I2:I2)</f>
+        <v>1000</v>
+      </c>
+      <c r="M4" s="0">
+        <f>SUM(M2+R2+S2+T2+U2+W2)-M3</f>
+        <v>1170</v>
+      </c>
+      <c r="N4" s="0">
+        <f>SUM(N2+R2+S2+T2+U2+W2)-N3</f>
+        <v>1170</v>
+      </c>
+      <c r="Q4" s="0">
+        <f>SUM(Q2:Q2)</f>
+        <v>1000</v>
+      </c>
+      <c r="R4" s="0">
+        <f>SUM(R2:R2)</f>
+        <v>90</v>
+      </c>
+      <c r="S4" s="0">
+        <f>SUM(S2:S2)</f>
+        <v>90</v>
+      </c>
+      <c r="T4" s="0">
+        <f>SUM(T2:T2)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="0">
+        <f>SUM(U2:U2)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="0">
+        <f>AC2-AC3</f>
+        <v>180</v>
+      </c>
+      <c r="AD4" t="s" s="0">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet104"/>
   <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12271,7 +12700,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
+    <col min="2" max="2" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="5" max="5" customWidth="true" width="19.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="F2" s="0">
+        <f>ROUND(C2*E2,2)</f>
+        <v>847.48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="1">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="F3" s="0">
+        <f>ROUND(C3*E3,2)</f>
+        <v>159.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet105"/>
   <dimension ref="A1:AG3"/>
@@ -12556,88 +13066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
-    <col min="2" max="2" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="5" max="5" customWidth="true" width="19.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>249</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>251</v>
-      </c>
-      <c r="F2" s="0">
-        <f>ROUND(C2*E2,2)</f>
-        <v>847.48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="1">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>252</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="F3" s="0">
-        <f>ROUND(C3*E3,2)</f>
-        <v>159.26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet106"/>
   <dimension ref="A1:AG4"/>
@@ -13025,7 +13454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet107"/>
   <dimension ref="A1:AI4"/>
@@ -13404,401 +13833,6 @@
       </c>
       <c r="U4" s="0">
         <f>SUM(U2:U3)</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="0">
-        <f>AC2-AC3</f>
-        <v>1170</v>
-      </c>
-      <c r="AD4" t="s" s="0">
-        <v>337</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet108"/>
-  <dimension ref="A1:AI4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="11" max="11" customWidth="true" width="21.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.7109375"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:35">
-      <c r="A1" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="J1" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="L1" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="M1" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="O1" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="P1" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q1" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="R1" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="S1" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="T1" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="U1" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="V1" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="W1" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="X1" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y1" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z1" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="AA1" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="AB1" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="AC1" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="AD1" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="AE1" s="0">
-        <v>1</v>
-      </c>
-      <c r="AF1" s="55" t="s">
-        <v>348</v>
-      </c>
-      <c r="AG1" s="54" t="s">
-        <v>347</v>
-      </c>
-      <c r="AH1" s="56" t="s">
-        <v>350</v>
-      </c>
-      <c r="AI1" s="56" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>339</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="M2" s="38">
-        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>1000</v>
-      </c>
-      <c r="N2" s="38">
-        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>1000</v>
-      </c>
-      <c r="O2" s="1">
-        <v>88363222</v>
-      </c>
-      <c r="P2" s="53">
-        <v>0.18</v>
-      </c>
-      <c r="Q2" s="1">
-        <f>M2</f>
-        <v>1000</v>
-      </c>
-      <c r="R2" s="1">
-        <f>IF(OR($AE$1=1,$AE$1=4),ROUND((Q2*P2)/2,2),0)</f>
-        <v>90</v>
-      </c>
-      <c r="S2" s="1">
-        <f>IF($AE$1=1,ROUND(((Q2*P2)/2),2),0)</f>
-        <v>90</v>
-      </c>
-      <c r="T2" s="1">
-        <f>IF($AE$1=2,ROUND(((Q2*P2)),2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U2" s="1">
-        <f>IF($AE$1=4,ROUND(((Q2*P2)/2),2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1">
-        <v>0</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="AA2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AB2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AC2" s="0">
-        <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)+R2+S2+T2+U2+W2),2)</f>
-        <v>1180</v>
-      </c>
-      <c r="AD2" t="s" s="0">
-        <v>337</v>
-      </c>
-      <c r="AE2" s="0">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>345</v>
-      </c>
-      <c r="AG2" t="s" s="0">
-        <v>346</v>
-      </c>
-      <c r="AH2" s="53">
-        <v>0.01</v>
-      </c>
-      <c r="AI2" s="1">
-        <f>Q2*AH2</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>349</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>339</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="I3" s="1">
-        <f>AI2</f>
-        <v>10</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="38">
-        <f>M2*1%</f>
-        <v>10</v>
-      </c>
-      <c r="N3" s="38">
-        <f>M2*1%</f>
-        <v>10</v>
-      </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="53">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1">
-        <f>IF(OR($AE$1=1,$AE$1=4),ROUND((Q3*P3)/2,2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S3" s="1">
-        <f>IF($AE$1=1,ROUND(((Q3*P3)/2),2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="1">
-        <f>IF($AE$1=2,ROUND(((Q3*P3)),2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="1">
-        <f>IF($AE$1=4,ROUND(((Q3*P3)/2),2),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V3" s="1">
-        <v>0</v>
-      </c>
-      <c r="W3" s="1">
-        <v>0</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="AA3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AB3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AC3" s="1">
-        <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)+R3+S3+T3+U3+W3),2)</f>
-        <v>10</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1"/>
-    </row>
-    <row r="4" spans="1:35">
-      <c r="I4" s="0">
-        <f>SUM(I2:I2)</f>
-        <v>1000</v>
-      </c>
-      <c r="M4" s="0">
-        <f>SUM(M2+R2+S2+T2+U2+W2)-M3</f>
-        <v>1170</v>
-      </c>
-      <c r="N4" s="0">
-        <f>SUM(N2+R2+S2+T2+U2+W2)-N3</f>
-        <v>1170</v>
-      </c>
-      <c r="Q4" s="0">
-        <f>SUM(Q2:Q2)</f>
-        <v>1000</v>
-      </c>
-      <c r="R4" s="0">
-        <f>SUM(R2:R2)</f>
-        <v>90</v>
-      </c>
-      <c r="S4" s="0">
-        <f>SUM(S2:S2)</f>
-        <v>90</v>
-      </c>
-      <c r="T4" s="0">
-        <f>SUM(T2:T2)</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="0">
-        <f>SUM(U2:U2)</f>
         <v>0</v>
       </c>
       <c r="AC4" s="0">
@@ -23187,10 +23221,10 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -23264,10 +23298,10 @@
         <v>303</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>

--- a/testdata/Financials.xlsx
+++ b/testdata/Financials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="136" activeTab="137"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="123" activeTab="125"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -131,37 +131,38 @@
     <sheet name="BPAdvJournalUSDNR" sheetId="150" r:id="rId122"/>
     <sheet name="JournalINRAdvNR" sheetId="144" r:id="rId123"/>
     <sheet name="BankReceipt" sheetId="35" r:id="rId124"/>
-    <sheet name="BankReceiptMulti" sheetId="37" r:id="rId125"/>
-    <sheet name="BRAdvUSDNR" sheetId="142" r:id="rId126"/>
-    <sheet name="BRAdvJournalUSDNR" sheetId="143" r:id="rId127"/>
-    <sheet name="BankReceiptUSD" sheetId="39" r:id="rId128"/>
-    <sheet name="BankReceiptMultiUSD" sheetId="40" r:id="rId129"/>
-    <sheet name="BankReceiptMulti (2)" sheetId="43" r:id="rId130"/>
-    <sheet name="BankReceiptMultiNewRef (2)" sheetId="44" r:id="rId131"/>
-    <sheet name="BankReceiptPDC" sheetId="56" r:id="rId132"/>
-    <sheet name="BankReceiptChargesUSD" sheetId="60" r:id="rId133"/>
-    <sheet name="BankReceiptCharges" sheetId="57" r:id="rId134"/>
-    <sheet name="BankPaymentChargesINR" sheetId="112" r:id="rId135"/>
-    <sheet name="BankPaymentCharges" sheetId="65" r:id="rId136"/>
-    <sheet name="BankPaymentExpGST" sheetId="63" r:id="rId137"/>
-    <sheet name="BankPaymentExpGSTTDS" sheetId="67" r:id="rId138"/>
-    <sheet name="BankPaymentExpUSD" sheetId="103" r:id="rId139"/>
-    <sheet name="BankPaymentExp" sheetId="62" r:id="rId140"/>
-    <sheet name="BankReceiptRevExp" sheetId="58" r:id="rId141"/>
-    <sheet name="BankPaymentExpTDS" sheetId="66" r:id="rId142"/>
-    <sheet name="BankPaymentPDC" sheetId="61" r:id="rId143"/>
-    <sheet name="BPAdvanceUSD" sheetId="161" r:id="rId144"/>
-    <sheet name="BPAdvance" sheetId="154" r:id="rId145"/>
-    <sheet name="BPJournalADV" sheetId="153" r:id="rId146"/>
-    <sheet name="TDS BPAdvance" sheetId="155" r:id="rId147"/>
-    <sheet name="TDS BPJournalADV" sheetId="156" r:id="rId148"/>
-    <sheet name="TDS BPAdvanceMulti" sheetId="157" r:id="rId149"/>
-    <sheet name="TDS BPJournalADVMulti" sheetId="158" r:id="rId150"/>
-    <sheet name="BPJournalADVINR" sheetId="159" r:id="rId151"/>
-    <sheet name="BPJournalADVUSD" sheetId="160" r:id="rId152"/>
-    <sheet name="BPMPMBADVNR" sheetId="162" r:id="rId153"/>
-    <sheet name="BPMPMBADVNRUSD" sheetId="163" r:id="rId154"/>
-    <sheet name="Sheet2" sheetId="146" r:id="rId155"/>
+    <sheet name="BankReceiptMultiCR" sheetId="168" r:id="rId125"/>
+    <sheet name="BankReceiptMulti" sheetId="37" r:id="rId126"/>
+    <sheet name="BRAdvUSDNR" sheetId="142" r:id="rId127"/>
+    <sheet name="BRAdvJournalUSDNR" sheetId="143" r:id="rId128"/>
+    <sheet name="BankReceiptUSD" sheetId="39" r:id="rId129"/>
+    <sheet name="BankReceiptMultiUSD" sheetId="40" r:id="rId130"/>
+    <sheet name="BankReceiptMulti (2)" sheetId="43" r:id="rId131"/>
+    <sheet name="BankReceiptMultiNewRef (2)" sheetId="44" r:id="rId132"/>
+    <sheet name="BankReceiptPDC" sheetId="56" r:id="rId133"/>
+    <sheet name="BankReceiptChargesUSD" sheetId="60" r:id="rId134"/>
+    <sheet name="BankReceiptCharges" sheetId="57" r:id="rId135"/>
+    <sheet name="BankPaymentChargesINR" sheetId="112" r:id="rId136"/>
+    <sheet name="BankPaymentCharges" sheetId="65" r:id="rId137"/>
+    <sheet name="BankPaymentExpGST" sheetId="63" r:id="rId138"/>
+    <sheet name="BankPaymentExpGSTTDS" sheetId="67" r:id="rId139"/>
+    <sheet name="BankPaymentExpUSD" sheetId="103" r:id="rId140"/>
+    <sheet name="BankPaymentExp" sheetId="62" r:id="rId141"/>
+    <sheet name="BankReceiptRevExp" sheetId="58" r:id="rId142"/>
+    <sheet name="BankPaymentExpTDS" sheetId="66" r:id="rId143"/>
+    <sheet name="BankPaymentPDC" sheetId="61" r:id="rId144"/>
+    <sheet name="BPAdvanceUSD" sheetId="161" r:id="rId145"/>
+    <sheet name="BPAdvance" sheetId="154" r:id="rId146"/>
+    <sheet name="BPJournalADV" sheetId="153" r:id="rId147"/>
+    <sheet name="TDS BPAdvance" sheetId="155" r:id="rId148"/>
+    <sheet name="TDS BPJournalADV" sheetId="156" r:id="rId149"/>
+    <sheet name="TDS BPAdvanceMulti" sheetId="157" r:id="rId150"/>
+    <sheet name="TDS BPJournalADVMulti" sheetId="158" r:id="rId151"/>
+    <sheet name="BPJournalADVINR" sheetId="159" r:id="rId152"/>
+    <sheet name="BPJournalADVUSD" sheetId="160" r:id="rId153"/>
+    <sheet name="BPMPMBADVNR" sheetId="162" r:id="rId154"/>
+    <sheet name="BPMPMBADVNRUSD" sheetId="163" r:id="rId155"/>
+    <sheet name="Sheet2" sheetId="146" r:id="rId156"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -181,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5626" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5591" uniqueCount="429">
   <si>
     <t>ITEM_NAME</t>
   </si>
@@ -8393,6 +8394,300 @@
 
 <file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AC4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="8.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="20.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="O1" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="P1" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="R1" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="S1" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="T1" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="U1" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="V1" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="W1" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="X1" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y1" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA1" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB1" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC1" s="40" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="M2" s="38">
+        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="38">
+        <f>AC2</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1">
+        <f>M2</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AC2" s="0">
+        <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" s="1" customFormat="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="M3" s="38">
+        <f>ROUND(SUM(AA3+AB3+I3),2)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="38">
+        <f>AC3</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>M3</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AB3" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="AC3" s="0">
+        <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="I4" s="0">
+        <f>SUM(I2:I3)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="0">
+        <f>SUM(M2:M3)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="0">
+        <f>SUM(N2:N3)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="0">
+        <f>SUM(AC2:AC3)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet93"/>
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8583,10 +8878,10 @@
         <v>276</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="AC2" s="0">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -8652,10 +8947,10 @@
         <v>276</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="AC3" s="0">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -8686,7 +8981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8917,7 +9212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9085,7 +9380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet94"/>
   <dimension ref="A1:AC3"/>
@@ -9317,7 +9612,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="25.5703125"/>
+    <col min="2" max="2" customWidth="true" width="15.140625"/>
+    <col min="3" max="3" customWidth="true" width="16.42578125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet95"/>
   <dimension ref="A1:AC4"/>
@@ -9632,56 +9976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" customWidth="true" width="25.5703125"/>
-    <col min="2" max="2" customWidth="true" width="15.140625"/>
-    <col min="3" max="3" customWidth="true" width="16.42578125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet96"/>
   <dimension ref="A1:AC4"/>
@@ -9961,7 +10256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet97"/>
   <dimension ref="A1:AC4"/>
@@ -10241,7 +10536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet98"/>
   <dimension ref="A1:AD3"/>
@@ -10477,7 +10772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet99"/>
   <dimension ref="A1:AD4"/>
@@ -10783,7 +11078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet135.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet100"/>
   <dimension ref="A1:AD4"/>
@@ -11089,7 +11384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet135.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet136.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet101"/>
   <dimension ref="A1:AD4"/>
@@ -11395,7 +11690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet136.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet102"/>
   <dimension ref="A1:AD4"/>
@@ -11701,7 +11996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet103"/>
   <dimension ref="A1:AG3"/>
@@ -11986,7 +12281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet108"/>
   <dimension ref="A1:AL4"/>
@@ -12415,7 +12710,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
+    <col min="2" max="2" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" customWidth="true" width="9.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="5" max="5" customWidth="true" width="19.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="F2" s="0">
+        <f>ROUND(C2*E2,2)</f>
+        <v>847.48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="1">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="F3" s="0">
+        <f>ROUND(C3*E3,2)</f>
+        <v>159.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet104"/>
   <dimension ref="A1:AG3"/>
@@ -12700,88 +13076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="24.85546875"/>
-    <col min="2" max="2" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="5" max="5" customWidth="true" width="19.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.28515625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>249</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>251</v>
-      </c>
-      <c r="F2" s="0">
-        <f>ROUND(C2*E2,2)</f>
-        <v>847.48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="1">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>252</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="F3" s="0">
-        <f>ROUND(C3*E3,2)</f>
-        <v>159.26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet105"/>
   <dimension ref="A1:AG3"/>
@@ -13066,7 +13361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet106"/>
   <dimension ref="A1:AG4"/>
@@ -13454,7 +13749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet143.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet107"/>
   <dimension ref="A1:AI4"/>
@@ -13849,7 +14144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet143.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet144.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet109"/>
   <dimension ref="A1:AD3"/>
@@ -14077,237 +14372,6 @@
       </c>
       <c r="AD3" s="1" t="s">
         <v>337</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet144.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="8" max="8" customWidth="true" width="17.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:29">
-      <c r="A1" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="J1" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="L1" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="M1" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="N1" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="O1" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="P1" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q1" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="R1" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="S1" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="T1" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="U1" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="V1" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="W1" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="X1" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y1" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z1" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="AA1" s="64" t="s">
-        <v>377</v>
-      </c>
-      <c r="AB1" s="64" t="s">
-        <v>378</v>
-      </c>
-      <c r="AC1" s="40" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="75" t="s">
-        <v>397</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>339</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="M2" s="38">
-        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="38">
-        <f>AC2</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1">
-        <f>M2</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AB2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AC2" s="0">
-        <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
-      <c r="M3" s="0">
-        <f>SUM(M2)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="0">
-        <f>SUM(N2)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="0">
-        <f>SUM(Q2)</f>
-        <v>0</v>
-      </c>
-      <c r="AA3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="0">
-        <f>SUM(AC2)</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14444,14 +14508,14 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="63" t="s">
-        <v>374</v>
+      <c r="B2" s="75" t="s">
+        <v>397</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>281</v>
@@ -14472,10 +14536,10 @@
         <v>276</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>319</v>
+        <v>369</v>
       </c>
       <c r="M2" s="38">
         <f>ROUND(SUM(AA2+AB2+I2),2)</f>
@@ -14548,6 +14612,237 @@
 </file>
 
 <file path=xl/worksheets/sheet146.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AC3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="29.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="8" max="8" customWidth="true" width="17.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.28515625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="25.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="O1" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="P1" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="R1" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="S1" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="T1" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="V1" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="W1" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="X1" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y1" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA1" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB1" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="AC1" s="40" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="M2" s="38">
+        <f>ROUND(SUM(AA2+AB2+I2),2)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="38">
+        <f>AC2</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1">
+        <f>M2</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AC2" s="0">
+        <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="M3" s="0">
+        <f>SUM(M2)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="0">
+        <f>SUM(N2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0">
+        <f>SUM(Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
+        <f>SUM(AC2)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14711,7 +15006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AH4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15045,7 +15340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15256,7 +15551,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet15"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="21.42578125"/>
+    <col min="2" max="2" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" customWidth="true" width="9.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet150.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AH6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15804,56 +16148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" customWidth="true" width="21.42578125"/>
-    <col min="2" max="2" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" customWidth="true" width="9.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet150.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet151.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AE11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16150,170 +16445,6 @@
       </c>
     </row>
     <row r="11" spans="1:31" ht="9" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet151.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="7" max="8" customWidth="true" width="18.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="10" max="10" customWidth="true" width="17.42578125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="13" max="13" customWidth="true" width="21.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>352</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>353</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>354</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>355</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2000000099</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I2" s="47">
-        <f>ROUND(SUM(G2+H2),2)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="59">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1001002003</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="I3" s="59">
-        <v>0</v>
-      </c>
-      <c r="J3" s="59">
-        <f>ROUND(SUM(G3+H3),2)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -16381,9 +16512,7 @@
       <c r="J1" s="56" t="s">
         <v>355</v>
       </c>
-      <c r="K1" t="s" s="0">
-        <v>369</v>
-      </c>
+      <c r="K1" s="37"/>
       <c r="L1" s="37"/>
       <c r="M1" s="37"/>
       <c r="N1" s="37"/>
@@ -16413,10 +16542,10 @@
         <v>191</v>
       </c>
       <c r="C2" s="1">
-        <v>2000000118</v>
+        <v>2000000099</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -16427,8 +16556,8 @@
         <v>310</v>
       </c>
       <c r="I2" s="47">
-        <f>ROUND(SUM(G2+H2)*K1,2)</f>
-        <v>15937.5</v>
+        <f>ROUND(SUM(G2+H2),2)</f>
+        <v>0</v>
       </c>
       <c r="J2" s="59">
         <v>0</v>
@@ -16459,10 +16588,10 @@
         <v>191</v>
       </c>
       <c r="C3" s="1">
-        <v>1001002001</v>
+        <v>1001002003</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -16476,8 +16605,8 @@
         <v>0</v>
       </c>
       <c r="J3" s="59">
-        <f>ROUND(SUM(G3+H3)*K1,2)</f>
-        <v>15937.5</v>
+        <f>ROUND(SUM(G3+H3),2)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -16487,6 +16616,172 @@
 </file>
 
 <file path=xl/worksheets/sheet153.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AE3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="33.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="7" max="8" customWidth="true" width="18.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="10" max="10" customWidth="true" width="17.42578125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="13" max="13" customWidth="true" width="21.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="20.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31">
+      <c r="A1" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>355</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2000000118</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="I2" s="47">
+        <f>ROUND(SUM(G2+H2)*K1,2)</f>
+        <v>15937.5</v>
+      </c>
+      <c r="J2" s="59">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1001002001</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="I3" s="59">
+        <v>0</v>
+      </c>
+      <c r="J3" s="59">
+        <f>ROUND(SUM(G3+H3)*K1,2)</f>
+        <v>15937.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16885,7 +17180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet155.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17284,7 +17579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet155.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24444,7 +24739,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>310</v>
+        <v>426</v>
       </c>
       <c r="AB2" t="s" s="0">
         <v>310</v>
@@ -37148,8 +37443,8 @@
       <c r="G2" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="H2" s="0">
-        <v>0</v>
+      <c r="H2" t="s" s="0">
+        <v>310</v>
       </c>
       <c r="I2" s="47">
         <f>ROUND(SUM(G2+H2),2)</f>
@@ -37194,8 +37489,8 @@
       <c r="G3" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="H3" s="0">
-        <v>0</v>
+      <c r="H3" t="s" s="0">
+        <v>310</v>
       </c>
       <c r="I3" s="59">
         <v>0</v>
